--- a/baseline/data_processing_elements-DSE.xlsx
+++ b/baseline/data_processing_elements-DSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85D40D7-6043-47B8-84F8-60A98C84F376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0D3DF5-FB93-415E-8CF6-B50DAF1BA63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="682">
   <si>
     <t>index</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t>Ethnicity - Caucasian/White</t>
-  </si>
-  <si>
-    <t>No race/ethnicity item collected. DOSES records only country of birth (Denmark vs other; MA1_A_S4 / MA1_B_S5), which is not equivalent to the DataSchema race-based ethnicity categories.</t>
   </si>
   <si>
     <t>impossible</t>
@@ -2733,13 +2730,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>9</v>
@@ -2787,7 +2784,7 @@
         <v>23</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2798,19 +2795,19 @@
         <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E2" t="s">
         <v>399</v>
-      </c>
-      <c r="E2" t="s">
-        <v>400</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M2" t="s">
         <v>26</v>
@@ -2854,13 +2851,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
@@ -2875,7 +2872,7 @@
         <v>37</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="120" x14ac:dyDescent="0.25">
@@ -2892,13 +2889,13 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
@@ -2913,7 +2910,7 @@
         <v>37</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -2930,13 +2927,13 @@
         <v>41</v>
       </c>
       <c r="E5" t="s">
+        <v>405</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="M5" t="s">
         <v>36</v>
@@ -2965,7 +2962,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -2977,10 +2974,10 @@
         <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="M6" t="s">
         <v>47</v>
@@ -3030,7 +3027,7 @@
         <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -3077,7 +3074,7 @@
         <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -3086,10 +3083,10 @@
         <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="M8" t="s">
         <v>65</v>
@@ -3130,25 +3127,25 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
         <v>71</v>
       </c>
       <c r="E9" t="s">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="M9" t="s">
         <v>72</v>
@@ -3181,7 +3178,7 @@
         <v>77</v>
       </c>
       <c r="AA9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3192,7 +3189,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
@@ -3204,13 +3201,13 @@
         <v>42</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M10" t="s">
         <v>72</v>
@@ -3243,7 +3240,7 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,40 +3257,37 @@
         <v>82</v>
       </c>
       <c r="E11" t="s">
+        <v>419</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
         <v>420</v>
       </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M11" t="s">
         <v>36</v>
       </c>
-      <c r="V11" t="s">
-        <v>83</v>
-      </c>
       <c r="W11" t="s">
+        <v>83</v>
+      </c>
+      <c r="X11" t="s">
         <v>84</v>
       </c>
-      <c r="X11" t="s">
-        <v>85</v>
-      </c>
       <c r="Y11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3304,46 +3298,43 @@
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" t="s">
         <v>424</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
         <v>425</v>
       </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M12" t="s">
         <v>36</v>
       </c>
-      <c r="V12" t="s">
-        <v>83</v>
-      </c>
       <c r="W12" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" t="s">
         <v>84</v>
       </c>
-      <c r="X12" t="s">
-        <v>85</v>
-      </c>
       <c r="Y12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3354,46 +3345,43 @@
         <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
       <c r="E13" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
         <v>428</v>
       </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M13" t="s">
         <v>36</v>
       </c>
-      <c r="V13" t="s">
-        <v>83</v>
-      </c>
       <c r="W13" t="s">
+        <v>83</v>
+      </c>
+      <c r="X13" t="s">
         <v>84</v>
       </c>
-      <c r="X13" t="s">
-        <v>85</v>
-      </c>
       <c r="Y13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3404,46 +3392,43 @@
         <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
         <v>89</v>
       </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
       <c r="E14" t="s">
+        <v>430</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" t="s">
         <v>431</v>
       </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
       </c>
-      <c r="V14" t="s">
-        <v>83</v>
-      </c>
       <c r="W14" t="s">
+        <v>83</v>
+      </c>
+      <c r="X14" t="s">
         <v>84</v>
       </c>
-      <c r="X14" t="s">
-        <v>85</v>
-      </c>
       <c r="Y14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3454,46 +3439,43 @@
         <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
         <v>91</v>
       </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
       <c r="E15" t="s">
+        <v>433</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
         <v>434</v>
       </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
       </c>
-      <c r="V15" t="s">
-        <v>83</v>
-      </c>
       <c r="W15" t="s">
+        <v>83</v>
+      </c>
+      <c r="X15" t="s">
         <v>84</v>
       </c>
-      <c r="X15" t="s">
-        <v>85</v>
-      </c>
       <c r="Y15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3504,46 +3486,43 @@
         <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
       <c r="E16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
         <v>437</v>
       </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M16" t="s">
         <v>36</v>
       </c>
-      <c r="V16" t="s">
-        <v>83</v>
-      </c>
       <c r="W16" t="s">
+        <v>83</v>
+      </c>
+      <c r="X16" t="s">
         <v>84</v>
       </c>
-      <c r="X16" t="s">
-        <v>85</v>
-      </c>
       <c r="Y16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3554,46 +3533,43 @@
         <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
         <v>95</v>
       </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
       <c r="E17" t="s">
+        <v>439</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
         <v>440</v>
       </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
       </c>
-      <c r="V17" t="s">
-        <v>83</v>
-      </c>
       <c r="W17" t="s">
+        <v>83</v>
+      </c>
+      <c r="X17" t="s">
         <v>84</v>
       </c>
-      <c r="X17" t="s">
-        <v>85</v>
-      </c>
       <c r="Y17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3604,46 +3580,43 @@
         <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
+        <v>442</v>
+      </c>
+      <c r="E18" t="s">
         <v>443</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" t="s">
         <v>444</v>
       </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
       </c>
-      <c r="V18" t="s">
-        <v>83</v>
-      </c>
       <c r="W18" t="s">
+        <v>83</v>
+      </c>
+      <c r="X18" t="s">
         <v>84</v>
       </c>
-      <c r="X18" t="s">
-        <v>85</v>
-      </c>
       <c r="Y18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3654,46 +3627,43 @@
         <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" t="s">
         <v>447</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
         <v>448</v>
       </c>
-      <c r="F19" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
       </c>
-      <c r="V19" t="s">
-        <v>83</v>
-      </c>
       <c r="W19" t="s">
+        <v>83</v>
+      </c>
+      <c r="X19" t="s">
         <v>84</v>
       </c>
-      <c r="X19" t="s">
-        <v>85</v>
-      </c>
       <c r="Y19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z19" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3704,29 +3674,29 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
         <v>99</v>
       </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
       <c r="E20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="M20" t="s">
         <v>36</v>
       </c>
       <c r="T20" s="1"/>
       <c r="V20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W20" t="s">
         <v>31</v>
@@ -3738,7 +3708,7 @@
         <v>37</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3749,34 +3719,34 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
         <v>102</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>103</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M21" t="s">
         <v>104</v>
       </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>105</v>
       </c>
-      <c r="N21" t="s">
+      <c r="P21" t="s">
         <v>106</v>
-      </c>
-      <c r="P21" t="s">
-        <v>107</v>
       </c>
       <c r="R21" t="s">
         <v>29</v>
@@ -3786,10 +3756,10 @@
       </c>
       <c r="T21" s="1"/>
       <c r="U21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="V21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W21" t="s">
         <v>31</v>
@@ -3801,7 +3771,7 @@
         <v>51</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
@@ -3812,28 +3782,28 @@
         <v>24</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>457</v>
+      </c>
+      <c r="E22" t="s">
+        <v>457</v>
+      </c>
+      <c r="F22" t="s">
         <v>110</v>
       </c>
-      <c r="D22" t="s">
-        <v>458</v>
-      </c>
-      <c r="E22" t="s">
-        <v>458</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>111</v>
       </c>
-      <c r="G22" t="s">
-        <v>112</v>
-      </c>
       <c r="M22" t="s">
+        <v>104</v>
+      </c>
+      <c r="N22" t="s">
         <v>105</v>
       </c>
-      <c r="N22" t="s">
+      <c r="P22" t="s">
         <v>106</v>
-      </c>
-      <c r="P22" t="s">
-        <v>107</v>
       </c>
       <c r="R22" t="s">
         <v>29</v>
@@ -3842,10 +3812,10 @@
         <v>68</v>
       </c>
       <c r="U22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="V22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W22" t="s">
         <v>31</v>
@@ -3868,25 +3838,25 @@
         <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
       </c>
       <c r="M23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s">
         <v>116</v>
       </c>
-      <c r="N23" t="s">
+      <c r="P23" t="s">
         <v>117</v>
-      </c>
-      <c r="P23" t="s">
-        <v>118</v>
       </c>
       <c r="R23" t="s">
         <v>29</v>
@@ -3895,10 +3865,10 @@
         <v>30</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="V23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W23" t="s">
         <v>31</v>
@@ -3910,7 +3880,7 @@
         <v>60</v>
       </c>
       <c r="Z23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3921,29 +3891,29 @@
         <v>24</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="s">
         <v>121</v>
       </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
       <c r="E24" t="s">
+        <v>458</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="M24" t="s">
         <v>36</v>
       </c>
       <c r="T24" s="1"/>
       <c r="V24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="W24" t="s">
         <v>31</v>
@@ -3955,7 +3925,7 @@
         <v>37</v>
       </c>
       <c r="Z24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="180" customHeight="1" x14ac:dyDescent="0.25">
@@ -3966,28 +3936,28 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
         <v>124</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>461</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="M25" t="s">
         <v>125</v>
       </c>
-      <c r="E25" t="s">
-        <v>462</v>
-      </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>126</v>
       </c>
-      <c r="N25" t="s">
+      <c r="P25" t="s">
         <v>127</v>
-      </c>
-      <c r="P25" t="s">
-        <v>128</v>
       </c>
       <c r="R25" t="s">
         <v>29</v>
@@ -3996,22 +3966,22 @@
         <v>30</v>
       </c>
       <c r="T25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="V25" t="s">
         <v>129</v>
       </c>
-      <c r="V25" t="s">
+      <c r="W25" t="s">
+        <v>83</v>
+      </c>
+      <c r="X25" t="s">
         <v>130</v>
       </c>
-      <c r="W25" t="s">
-        <v>84</v>
-      </c>
-      <c r="X25" t="s">
-        <v>131</v>
-      </c>
       <c r="Y25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z25" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,43 +3992,43 @@
         <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" t="s">
+        <v>463</v>
+      </c>
+      <c r="E26" t="s">
+        <v>464</v>
+      </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="M26" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" t="s">
         <v>132</v>
       </c>
-      <c r="D26" t="s">
-        <v>464</v>
-      </c>
-      <c r="E26" t="s">
-        <v>465</v>
-      </c>
-      <c r="F26" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="M26" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" t="s">
-        <v>133</v>
-      </c>
       <c r="W26" t="s">
+        <v>83</v>
+      </c>
+      <c r="X26" t="s">
         <v>84</v>
       </c>
-      <c r="X26" t="s">
-        <v>85</v>
-      </c>
       <c r="Y26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4069,34 +4039,34 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D27" t="s">
+        <v>468</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="K27" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="N27" t="s">
         <v>135</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="P27" t="s">
         <v>136</v>
-      </c>
-      <c r="P27" t="s">
-        <v>137</v>
       </c>
       <c r="R27" t="s">
         <v>29</v>
@@ -4105,7 +4075,7 @@
         <v>68</v>
       </c>
       <c r="U27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W27" t="s">
         <v>31</v>
@@ -4117,7 +4087,7 @@
         <v>76</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,28 +4098,28 @@
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D28" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" t="s">
+        <v>471</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="E28" t="s">
-        <v>472</v>
-      </c>
-      <c r="F28" t="s">
-        <v>42</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N28" t="s">
+        <v>135</v>
+      </c>
+      <c r="P28" t="s">
         <v>136</v>
-      </c>
-      <c r="P28" t="s">
-        <v>137</v>
       </c>
       <c r="R28" t="s">
         <v>29</v>
@@ -4158,7 +4128,7 @@
         <v>68</v>
       </c>
       <c r="U28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W28" t="s">
         <v>31</v>
@@ -4170,7 +4140,7 @@
         <v>76</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4181,34 +4151,34 @@
         <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" t="s">
         <v>138</v>
       </c>
-      <c r="F29" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="J29" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="N29" t="s">
         <v>139</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="N29" t="s">
+      <c r="P29" t="s">
         <v>140</v>
-      </c>
-      <c r="P29" t="s">
-        <v>141</v>
       </c>
       <c r="R29" t="s">
         <v>29</v>
@@ -4217,7 +4187,7 @@
         <v>68</v>
       </c>
       <c r="U29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W29" t="s">
         <v>31</v>
@@ -4229,7 +4199,7 @@
         <v>76</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4240,28 +4210,28 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N30" t="s">
+        <v>139</v>
+      </c>
+      <c r="P30" t="s">
         <v>140</v>
-      </c>
-      <c r="P30" t="s">
-        <v>141</v>
       </c>
       <c r="R30" t="s">
         <v>29</v>
@@ -4270,7 +4240,7 @@
         <v>68</v>
       </c>
       <c r="U30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W30" t="s">
         <v>31</v>
@@ -4282,7 +4252,7 @@
         <v>76</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4293,34 +4263,34 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D31" t="s">
+        <v>475</v>
+      </c>
+      <c r="E31" t="s">
         <v>476</v>
       </c>
-      <c r="E31" t="s">
-        <v>477</v>
-      </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G31" t="s">
+        <v>141</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M31" t="s">
         <v>142</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>143</v>
       </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>144</v>
-      </c>
-      <c r="P31" t="s">
-        <v>145</v>
       </c>
       <c r="R31" t="s">
         <v>29</v>
@@ -4329,10 +4299,10 @@
         <v>68</v>
       </c>
       <c r="U31" t="s">
+        <v>145</v>
+      </c>
+      <c r="V31" t="s">
         <v>146</v>
-      </c>
-      <c r="V31" t="s">
-        <v>147</v>
       </c>
       <c r="W31" t="s">
         <v>31</v>
@@ -4344,7 +4314,7 @@
         <v>76</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4355,43 +4325,43 @@
         <v>24</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" t="s">
+        <v>477</v>
+      </c>
+      <c r="F32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M32" t="s">
+        <v>36</v>
+      </c>
+      <c r="V32" t="s">
         <v>148</v>
       </c>
-      <c r="E32" t="s">
-        <v>478</v>
-      </c>
-      <c r="F32" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" t="s">
-        <v>135</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M32" t="s">
-        <v>36</v>
-      </c>
-      <c r="V32" t="s">
-        <v>149</v>
-      </c>
       <c r="W32" t="s">
+        <v>83</v>
+      </c>
+      <c r="X32" t="s">
         <v>84</v>
       </c>
-      <c r="X32" t="s">
-        <v>85</v>
-      </c>
       <c r="Y32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z32" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4402,37 +4372,37 @@
         <v>24</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M33" t="s">
         <v>36</v>
       </c>
       <c r="V33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W33" t="s">
+        <v>83</v>
+      </c>
+      <c r="X33" t="s">
         <v>84</v>
       </c>
-      <c r="X33" t="s">
-        <v>85</v>
-      </c>
       <c r="Y33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z33" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -4443,28 +4413,28 @@
         <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F34" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" t="s">
         <v>150</v>
       </c>
-      <c r="E34" t="s">
-        <v>480</v>
-      </c>
-      <c r="F34" t="s">
-        <v>111</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="M34" t="s">
         <v>151</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>152</v>
       </c>
-      <c r="N34" t="s">
+      <c r="P34" t="s">
         <v>153</v>
-      </c>
-      <c r="P34" t="s">
-        <v>154</v>
       </c>
       <c r="R34" t="s">
         <v>29</v>
@@ -4473,7 +4443,7 @@
         <v>68</v>
       </c>
       <c r="U34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="W34" t="s">
         <v>31</v>
@@ -4496,25 +4466,25 @@
         <v>24</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F35" t="s">
         <v>42</v>
       </c>
       <c r="M35" t="s">
+        <v>151</v>
+      </c>
+      <c r="N35" t="s">
         <v>152</v>
       </c>
-      <c r="N35" t="s">
+      <c r="P35" t="s">
         <v>153</v>
-      </c>
-      <c r="P35" t="s">
-        <v>154</v>
       </c>
       <c r="R35" t="s">
         <v>29</v>
@@ -4523,10 +4493,10 @@
         <v>68</v>
       </c>
       <c r="U35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="W35" t="s">
         <v>31</v>
@@ -4538,7 +4508,7 @@
         <v>51</v>
       </c>
       <c r="Z35" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4549,34 +4519,34 @@
         <v>24</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D36" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" t="s">
+        <v>481</v>
+      </c>
+      <c r="F36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" t="s">
         <v>155</v>
       </c>
-      <c r="E36" t="s">
+      <c r="J36" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="K36" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="N36" t="s">
         <v>156</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="P36" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="R36" t="s">
         <v>29</v>
@@ -4585,10 +4555,10 @@
         <v>68</v>
       </c>
       <c r="U36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W36" t="s">
         <v>31</v>
@@ -4600,7 +4570,7 @@
         <v>51</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4611,34 +4581,34 @@
         <v>24</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" t="s">
+        <v>484</v>
+      </c>
+      <c r="F37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" t="s">
+        <v>155</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="N37" t="s">
         <v>159</v>
       </c>
-      <c r="E37" t="s">
-        <v>485</v>
-      </c>
-      <c r="F37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="N37" t="s">
+      <c r="P37" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="R37" t="s">
         <v>29</v>
@@ -4647,10 +4617,10 @@
         <v>68</v>
       </c>
       <c r="U37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V37" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W37" t="s">
         <v>31</v>
@@ -4662,7 +4632,7 @@
         <v>70</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4673,34 +4643,34 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>485</v>
+      </c>
+      <c r="F38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" t="s">
         <v>162</v>
       </c>
-      <c r="E38" t="s">
+      <c r="J38" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F38" t="s">
-        <v>111</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="M38" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="N38" t="s">
         <v>163</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="P38" t="s">
         <v>164</v>
-      </c>
-      <c r="P38" t="s">
-        <v>165</v>
       </c>
       <c r="R38" t="s">
         <v>29</v>
@@ -4709,10 +4679,10 @@
         <v>68</v>
       </c>
       <c r="U38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V38" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W38" t="s">
         <v>31</v>
@@ -4724,7 +4694,7 @@
         <v>70</v>
       </c>
       <c r="Z38" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,44 +4705,44 @@
         <v>24</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D39" t="s">
+        <v>487</v>
+      </c>
+      <c r="E39" t="s">
+        <v>487</v>
+      </c>
+      <c r="F39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" t="s">
+        <v>166</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="E39" t="s">
-        <v>488</v>
-      </c>
-      <c r="F39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="M39" t="s">
         <v>36</v>
       </c>
       <c r="P39" s="1"/>
       <c r="V39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W39" t="s">
+        <v>83</v>
+      </c>
+      <c r="X39" t="s">
         <v>84</v>
       </c>
-      <c r="X39" t="s">
-        <v>85</v>
-      </c>
       <c r="Y39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z39" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4783,37 +4753,37 @@
         <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" t="s">
+        <v>490</v>
+      </c>
+      <c r="E40" t="s">
+        <v>491</v>
+      </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" t="s">
         <v>169</v>
       </c>
-      <c r="D40" t="s">
-        <v>491</v>
-      </c>
-      <c r="E40" t="s">
-        <v>492</v>
-      </c>
-      <c r="F40" t="s">
-        <v>42</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="M40" t="s">
-        <v>36</v>
-      </c>
-      <c r="V40" t="s">
-        <v>170</v>
-      </c>
       <c r="W40" t="s">
+        <v>83</v>
+      </c>
+      <c r="X40" t="s">
         <v>84</v>
       </c>
-      <c r="X40" t="s">
-        <v>85</v>
-      </c>
       <c r="Y40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z40" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -4824,37 +4794,37 @@
         <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D41" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E41" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M41" t="s">
         <v>36</v>
       </c>
       <c r="V41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W41" t="s">
+        <v>83</v>
+      </c>
+      <c r="X41" t="s">
         <v>84</v>
       </c>
-      <c r="X41" t="s">
-        <v>85</v>
-      </c>
       <c r="Y41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z41" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
@@ -4865,37 +4835,37 @@
         <v>24</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s">
         <v>36</v>
       </c>
       <c r="V42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W42" t="s">
+        <v>83</v>
+      </c>
+      <c r="X42" t="s">
         <v>84</v>
       </c>
-      <c r="X42" t="s">
-        <v>85</v>
-      </c>
       <c r="Y42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
@@ -4906,37 +4876,37 @@
         <v>24</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" t="s">
         <v>173</v>
       </c>
-      <c r="E43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" t="s">
-        <v>111</v>
-      </c>
-      <c r="G43" t="s">
-        <v>174</v>
-      </c>
       <c r="M43" t="s">
         <v>36</v>
       </c>
       <c r="V43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W43" t="s">
+        <v>83</v>
+      </c>
+      <c r="X43" t="s">
         <v>84</v>
       </c>
-      <c r="X43" t="s">
-        <v>85</v>
-      </c>
       <c r="Y43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z43" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
@@ -4947,37 +4917,37 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M44" t="s">
         <v>36</v>
       </c>
       <c r="V44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W44" t="s">
+        <v>83</v>
+      </c>
+      <c r="X44" t="s">
         <v>84</v>
       </c>
-      <c r="X44" t="s">
-        <v>85</v>
-      </c>
       <c r="Y44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
@@ -4988,37 +4958,37 @@
         <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E45" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M45" t="s">
         <v>36</v>
       </c>
       <c r="V45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W45" t="s">
+        <v>83</v>
+      </c>
+      <c r="X45" t="s">
         <v>84</v>
       </c>
-      <c r="X45" t="s">
-        <v>85</v>
-      </c>
       <c r="Y45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z45" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="180" customHeight="1" x14ac:dyDescent="0.25">
@@ -5029,41 +4999,41 @@
         <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
+        <v>497</v>
+      </c>
+      <c r="E46" t="s">
+        <v>497</v>
+      </c>
+      <c r="F46" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" t="s">
+        <v>173</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="E46" t="s">
-        <v>498</v>
-      </c>
-      <c r="F46" t="s">
-        <v>111</v>
-      </c>
-      <c r="G46" t="s">
-        <v>174</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N46" s="1"/>
       <c r="V46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W46" t="s">
+        <v>83</v>
+      </c>
+      <c r="X46" t="s">
         <v>84</v>
       </c>
-      <c r="X46" t="s">
-        <v>85</v>
-      </c>
       <c r="Y46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z46" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -5074,37 +5044,37 @@
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M47" t="s">
         <v>36</v>
       </c>
       <c r="V47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W47" t="s">
+        <v>83</v>
+      </c>
+      <c r="X47" t="s">
         <v>84</v>
       </c>
-      <c r="X47" t="s">
-        <v>85</v>
-      </c>
       <c r="Y47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -5115,37 +5085,37 @@
         <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M48" t="s">
         <v>36</v>
       </c>
       <c r="V48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W48" t="s">
+        <v>83</v>
+      </c>
+      <c r="X48" t="s">
         <v>84</v>
       </c>
-      <c r="X48" t="s">
-        <v>85</v>
-      </c>
       <c r="Y48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5156,43 +5126,43 @@
         <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" t="s">
+        <v>500</v>
+      </c>
+      <c r="E49" t="s">
+        <v>500</v>
+      </c>
+      <c r="F49" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" t="s">
         <v>180</v>
       </c>
-      <c r="D49" t="s">
+      <c r="J49" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E49" t="s">
-        <v>501</v>
-      </c>
-      <c r="F49" t="s">
-        <v>111</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="K49" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" t="s">
         <v>181</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M49" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" t="s">
-        <v>182</v>
-      </c>
       <c r="W49" t="s">
+        <v>83</v>
+      </c>
+      <c r="X49" t="s">
         <v>84</v>
       </c>
-      <c r="X49" t="s">
-        <v>85</v>
-      </c>
       <c r="Y49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z49" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5203,40 +5173,40 @@
         <v>24</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D50" t="s">
+        <v>503</v>
+      </c>
+      <c r="E50" t="s">
+        <v>503</v>
+      </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E50" t="s">
-        <v>504</v>
-      </c>
-      <c r="F50" t="s">
-        <v>42</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="M50" t="s">
         <v>36</v>
       </c>
       <c r="V50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W50" t="s">
+        <v>83</v>
+      </c>
+      <c r="X50" t="s">
         <v>84</v>
       </c>
-      <c r="X50" t="s">
-        <v>85</v>
-      </c>
       <c r="Y50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z50" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="45" x14ac:dyDescent="0.25">
@@ -5247,43 +5217,43 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D51" t="s">
+        <v>506</v>
+      </c>
+      <c r="E51" t="s">
+        <v>506</v>
+      </c>
+      <c r="F51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G51" t="s">
+        <v>180</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="E51" t="s">
-        <v>507</v>
-      </c>
-      <c r="F51" t="s">
-        <v>111</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="K51" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="M51" t="s">
+        <v>36</v>
+      </c>
+      <c r="V51" t="s">
         <v>181</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="M51" t="s">
-        <v>36</v>
-      </c>
-      <c r="V51" t="s">
-        <v>182</v>
-      </c>
       <c r="W51" t="s">
+        <v>83</v>
+      </c>
+      <c r="X51" t="s">
         <v>84</v>
       </c>
-      <c r="X51" t="s">
-        <v>85</v>
-      </c>
       <c r="Y51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z51" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -5294,44 +5264,44 @@
         <v>24</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D52" t="s">
+        <v>509</v>
+      </c>
+      <c r="E52" t="s">
+        <v>509</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E52" t="s">
-        <v>510</v>
-      </c>
-      <c r="F52" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="L52" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M52" t="s">
         <v>36</v>
       </c>
       <c r="T52" s="1"/>
       <c r="V52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W52" t="s">
+        <v>83</v>
+      </c>
+      <c r="X52" t="s">
         <v>84</v>
       </c>
-      <c r="X52" t="s">
-        <v>85</v>
-      </c>
       <c r="Y52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -5342,37 +5312,37 @@
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" t="s">
+        <v>185</v>
+      </c>
+      <c r="F53" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" t="s">
         <v>186</v>
       </c>
-      <c r="E53" t="s">
-        <v>186</v>
-      </c>
-      <c r="F53" t="s">
-        <v>111</v>
-      </c>
-      <c r="G53" t="s">
-        <v>187</v>
-      </c>
       <c r="M53" t="s">
         <v>36</v>
       </c>
       <c r="V53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W53" t="s">
+        <v>83</v>
+      </c>
+      <c r="X53" t="s">
         <v>84</v>
       </c>
-      <c r="X53" t="s">
-        <v>85</v>
-      </c>
       <c r="Y53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z53" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5383,44 +5353,44 @@
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" t="s">
+        <v>512</v>
+      </c>
+      <c r="E54" t="s">
+        <v>512</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
+      <c r="J54" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="E54" t="s">
-        <v>513</v>
-      </c>
-      <c r="F54" t="s">
-        <v>111</v>
-      </c>
-      <c r="G54" t="s">
-        <v>189</v>
-      </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="M54" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="1"/>
       <c r="V54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W54" t="s">
+        <v>83</v>
+      </c>
+      <c r="X54" t="s">
         <v>84</v>
       </c>
-      <c r="X54" t="s">
-        <v>85</v>
-      </c>
       <c r="Y54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z54" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -5431,37 +5401,37 @@
         <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" t="s">
+        <v>515</v>
+      </c>
+      <c r="E55" t="s">
+        <v>515</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="M55" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" t="s">
         <v>191</v>
       </c>
-      <c r="D55" t="s">
-        <v>516</v>
-      </c>
-      <c r="E55" t="s">
-        <v>516</v>
-      </c>
-      <c r="F55" t="s">
-        <v>42</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="M55" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55" t="s">
-        <v>192</v>
-      </c>
       <c r="W55" t="s">
+        <v>83</v>
+      </c>
+      <c r="X55" t="s">
         <v>84</v>
       </c>
-      <c r="X55" t="s">
-        <v>85</v>
-      </c>
       <c r="Y55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z55" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="270" customHeight="1" x14ac:dyDescent="0.25">
@@ -5472,34 +5442,34 @@
         <v>24</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D56" t="s">
         <v>193</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>193</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="M56" t="s">
+        <v>667</v>
+      </c>
+      <c r="N56" t="s">
         <v>194</v>
       </c>
-      <c r="E56" t="s">
-        <v>194</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="M56" t="s">
-        <v>668</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="P56" t="s">
         <v>195</v>
-      </c>
-      <c r="P56" t="s">
-        <v>196</v>
       </c>
       <c r="R56" t="s">
         <v>29</v>
@@ -5508,10 +5478,10 @@
         <v>30</v>
       </c>
       <c r="T56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="V56" t="s">
         <v>197</v>
-      </c>
-      <c r="V56" t="s">
-        <v>198</v>
       </c>
       <c r="W56" t="s">
         <v>31</v>
@@ -5523,7 +5493,7 @@
         <v>76</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -5534,31 +5504,31 @@
         <v>24</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D57" t="s">
         <v>199</v>
       </c>
-      <c r="D57" t="s">
-        <v>200</v>
-      </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" t="s">
         <v>42</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M57" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N57" t="s">
+        <v>194</v>
+      </c>
+      <c r="P57" t="s">
         <v>195</v>
-      </c>
-      <c r="P57" t="s">
-        <v>196</v>
       </c>
       <c r="R57" t="s">
         <v>29</v>
@@ -5567,10 +5537,10 @@
         <v>30</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="W57" t="s">
         <v>31</v>
@@ -5582,7 +5552,7 @@
         <v>76</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="240" customHeight="1" x14ac:dyDescent="0.25">
@@ -5593,43 +5563,43 @@
         <v>24</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D58" t="s">
+        <v>521</v>
+      </c>
+      <c r="E58" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" t="s">
+        <v>110</v>
+      </c>
+      <c r="G58" t="s">
         <v>202</v>
       </c>
-      <c r="D58" t="s">
+      <c r="J58" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E58" t="s">
-        <v>522</v>
-      </c>
-      <c r="F58" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="K58" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="M58" t="s">
+        <v>36</v>
+      </c>
+      <c r="V58" t="s">
         <v>203</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="M58" t="s">
-        <v>36</v>
-      </c>
-      <c r="V58" t="s">
-        <v>204</v>
-      </c>
       <c r="W58" t="s">
+        <v>83</v>
+      </c>
+      <c r="X58" t="s">
         <v>84</v>
       </c>
-      <c r="X58" t="s">
-        <v>85</v>
-      </c>
       <c r="Y58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z58" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -5640,19 +5610,19 @@
         <v>24</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D59" t="s">
         <v>205</v>
       </c>
-      <c r="D59" t="s">
-        <v>206</v>
-      </c>
       <c r="E59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F59" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" t="s">
         <v>111</v>
-      </c>
-      <c r="G59" t="s">
-        <v>112</v>
       </c>
       <c r="M59" t="s">
         <v>36</v>
@@ -5660,19 +5630,19 @@
       <c r="R59" s="1"/>
       <c r="T59" s="1"/>
       <c r="V59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W59" t="s">
+        <v>83</v>
+      </c>
+      <c r="X59" t="s">
         <v>84</v>
       </c>
-      <c r="X59" t="s">
-        <v>85</v>
-      </c>
       <c r="Y59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z59" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="390" customHeight="1" x14ac:dyDescent="0.25">
@@ -5683,22 +5653,22 @@
         <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" t="s">
         <v>208</v>
       </c>
-      <c r="D60" t="s">
-        <v>209</v>
-      </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F60" t="s">
         <v>42</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="M60" t="s">
         <v>36</v>
@@ -5706,19 +5676,19 @@
       <c r="R60" s="1"/>
       <c r="T60" s="1"/>
       <c r="V60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W60" t="s">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s">
         <v>84</v>
       </c>
-      <c r="X60" t="s">
-        <v>85</v>
-      </c>
       <c r="Y60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z60" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5729,22 +5699,22 @@
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
+        <v>525</v>
+      </c>
+      <c r="E61" t="s">
         <v>526</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F61" t="s">
-        <v>42</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="M61" t="s">
         <v>36</v>
@@ -5753,19 +5723,19 @@
       <c r="R61" s="1"/>
       <c r="T61" s="1"/>
       <c r="V61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W61" t="s">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s">
         <v>84</v>
       </c>
-      <c r="X61" t="s">
-        <v>85</v>
-      </c>
       <c r="Y61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z61" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5776,40 +5746,40 @@
         <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D62" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E62" t="s">
-        <v>212</v>
-      </c>
-      <c r="F62" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="L62" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M62" t="s">
+        <v>36</v>
+      </c>
+      <c r="V62" t="s">
         <v>213</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M62" t="s">
-        <v>36</v>
-      </c>
-      <c r="V62" t="s">
-        <v>214</v>
-      </c>
       <c r="W62" t="s">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s">
         <v>84</v>
       </c>
-      <c r="X62" t="s">
-        <v>85</v>
-      </c>
       <c r="Y62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5820,38 +5790,38 @@
         <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D63" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E63" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F63" t="s">
         <v>42</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M63" t="s">
         <v>36</v>
       </c>
       <c r="R63" s="1"/>
       <c r="V63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W63" t="s">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s">
         <v>84</v>
       </c>
-      <c r="X63" t="s">
-        <v>85</v>
-      </c>
       <c r="Y63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5862,37 +5832,37 @@
         <v>24</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D64" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E64" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F64" t="s">
         <v>42</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M64" t="s">
         <v>36</v>
       </c>
       <c r="V64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W64" t="s">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s">
         <v>84</v>
       </c>
-      <c r="X64" t="s">
-        <v>85</v>
-      </c>
       <c r="Y64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5903,38 +5873,38 @@
         <v>24</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D65" t="s">
+        <v>532</v>
+      </c>
+      <c r="E65" t="s">
         <v>533</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="F65" t="s">
-        <v>42</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="M65" t="s">
         <v>36</v>
       </c>
       <c r="R65" s="1"/>
       <c r="V65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W65" t="s">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s">
         <v>84</v>
       </c>
-      <c r="X65" t="s">
-        <v>85</v>
-      </c>
       <c r="Y65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z65" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -5945,40 +5915,40 @@
         <v>24</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>535</v>
+      </c>
+      <c r="E66" t="s">
         <v>215</v>
       </c>
-      <c r="D66" t="s">
-        <v>536</v>
-      </c>
-      <c r="E66" t="s">
-        <v>216</v>
-      </c>
       <c r="F66" t="s">
         <v>42</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M66" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" t="s">
         <v>213</v>
       </c>
-      <c r="L66" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M66" t="s">
-        <v>36</v>
-      </c>
-      <c r="V66" t="s">
-        <v>214</v>
-      </c>
       <c r="W66" t="s">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s">
         <v>84</v>
       </c>
-      <c r="X66" t="s">
-        <v>85</v>
-      </c>
       <c r="Y66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z66" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -5989,40 +5959,40 @@
         <v>24</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D67" t="s">
+        <v>536</v>
+      </c>
+      <c r="E67" t="s">
         <v>217</v>
       </c>
-      <c r="D67" t="s">
-        <v>537</v>
-      </c>
-      <c r="E67" t="s">
-        <v>218</v>
-      </c>
       <c r="F67" t="s">
         <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M67" t="s">
+        <v>36</v>
+      </c>
+      <c r="V67" t="s">
         <v>213</v>
       </c>
-      <c r="L67" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M67" t="s">
-        <v>36</v>
-      </c>
-      <c r="V67" t="s">
-        <v>214</v>
-      </c>
       <c r="W67" t="s">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s">
         <v>84</v>
       </c>
-      <c r="X67" t="s">
-        <v>85</v>
-      </c>
       <c r="Y67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z67" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6033,22 +6003,22 @@
         <v>24</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D68" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E68" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F68" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" t="s">
         <v>111</v>
       </c>
-      <c r="G68" t="s">
-        <v>112</v>
-      </c>
       <c r="J68" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M68" t="s">
         <v>36</v>
@@ -6057,19 +6027,19 @@
       <c r="P68" s="1"/>
       <c r="R68" s="1"/>
       <c r="V68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W68" t="s">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s">
         <v>84</v>
       </c>
-      <c r="X68" t="s">
-        <v>85</v>
-      </c>
       <c r="Y68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z68" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6080,19 +6050,19 @@
         <v>24</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E69" t="s">
+        <v>538</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="F69" t="s">
-        <v>42</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="M69" t="s">
         <v>36</v>
@@ -6101,19 +6071,19 @@
       <c r="P69" s="1"/>
       <c r="R69" s="1"/>
       <c r="V69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W69" t="s">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s">
         <v>84</v>
       </c>
-      <c r="X69" t="s">
-        <v>85</v>
-      </c>
       <c r="Y69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z69" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -6124,31 +6094,31 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D70" t="s">
+        <v>540</v>
+      </c>
+      <c r="E70" t="s">
         <v>541</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F70" t="s">
-        <v>42</v>
-      </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="M70" t="s">
+        <v>317</v>
+      </c>
+      <c r="N70" t="s">
         <v>318</v>
       </c>
-      <c r="N70" t="s">
+      <c r="P70" t="s">
         <v>319</v>
-      </c>
-      <c r="P70" t="s">
-        <v>320</v>
       </c>
       <c r="R70" t="s">
         <v>29</v>
@@ -6157,22 +6127,22 @@
         <v>30</v>
       </c>
       <c r="T70" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V70" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="W70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z70" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:26" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -6183,40 +6153,40 @@
         <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D71" t="s">
+        <v>321</v>
+      </c>
+      <c r="E71" t="s">
         <v>322</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M71" t="s">
+        <v>36</v>
+      </c>
+      <c r="V71" t="s">
         <v>323</v>
       </c>
-      <c r="F71" t="s">
-        <v>42</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="M71" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" t="s">
-        <v>324</v>
-      </c>
       <c r="W71" t="s">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s">
         <v>84</v>
       </c>
-      <c r="X71" t="s">
-        <v>85</v>
-      </c>
       <c r="Y71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z71" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6227,34 +6197,34 @@
         <v>24</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E72" t="s">
+        <v>545</v>
+      </c>
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M72" t="s">
         <v>325</v>
       </c>
-      <c r="E72" t="s">
-        <v>546</v>
-      </c>
-      <c r="F72" t="s">
-        <v>42</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>326</v>
       </c>
-      <c r="N72" t="s">
+      <c r="P72" t="s">
         <v>327</v>
-      </c>
-      <c r="P72" t="s">
-        <v>328</v>
       </c>
       <c r="R72" t="s">
         <v>29</v>
@@ -6263,22 +6233,22 @@
         <v>30</v>
       </c>
       <c r="T72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="V72" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="W72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z72" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:26" ht="285" customHeight="1" x14ac:dyDescent="0.25">
@@ -6289,41 +6259,41 @@
         <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E73" t="s">
+        <v>547</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F73" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="L73" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s">
         <v>36</v>
       </c>
       <c r="T73" s="1"/>
       <c r="V73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="W73" t="s">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s">
         <v>84</v>
       </c>
-      <c r="X73" t="s">
-        <v>85</v>
-      </c>
       <c r="Y73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z73" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6334,34 +6304,34 @@
         <v>24</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D74" t="s">
+        <v>332</v>
+      </c>
+      <c r="E74" t="s">
+        <v>549</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M74" t="s">
         <v>333</v>
       </c>
-      <c r="E74" t="s">
-        <v>550</v>
-      </c>
-      <c r="F74" t="s">
-        <v>42</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>334</v>
       </c>
-      <c r="N74" t="s">
+      <c r="P74" t="s">
         <v>335</v>
-      </c>
-      <c r="P74" t="s">
-        <v>336</v>
       </c>
       <c r="R74" t="s">
         <v>29</v>
@@ -6370,10 +6340,10 @@
         <v>30</v>
       </c>
       <c r="T74" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="V74" t="s">
         <v>337</v>
-      </c>
-      <c r="V74" t="s">
-        <v>338</v>
       </c>
       <c r="W74" t="s">
         <v>31</v>
@@ -6385,7 +6355,7 @@
         <v>60</v>
       </c>
       <c r="Z74" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6396,37 +6366,37 @@
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D75" t="s">
+        <v>551</v>
+      </c>
+      <c r="E75" t="s">
         <v>552</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
+        <v>110</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F75" t="s">
-        <v>111</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="M75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="W75" t="s">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s">
         <v>84</v>
       </c>
-      <c r="X75" t="s">
-        <v>85</v>
-      </c>
       <c r="Y75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z75" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:26" ht="270" customHeight="1" x14ac:dyDescent="0.25">
@@ -6437,37 +6407,37 @@
         <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D76" t="s">
+        <v>554</v>
+      </c>
+      <c r="E76" t="s">
         <v>555</v>
       </c>
-      <c r="E76" t="s">
-        <v>556</v>
-      </c>
       <c r="F76" t="s">
         <v>42</v>
       </c>
       <c r="G76" t="s">
+        <v>339</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V76" t="s">
         <v>340</v>
       </c>
-      <c r="M76" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V76" t="s">
-        <v>341</v>
-      </c>
       <c r="W76" t="s">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s">
         <v>84</v>
       </c>
-      <c r="X76" t="s">
-        <v>85</v>
-      </c>
       <c r="Y76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z76" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:26" ht="390" customHeight="1" x14ac:dyDescent="0.25">
@@ -6478,31 +6448,31 @@
         <v>24</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" t="s">
+        <v>556</v>
+      </c>
+      <c r="E77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F77" t="s">
+        <v>42</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="N77" t="s">
         <v>220</v>
       </c>
-      <c r="D77" t="s">
-        <v>557</v>
-      </c>
-      <c r="E77" t="s">
-        <v>557</v>
-      </c>
-      <c r="F77" t="s">
-        <v>42</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="N77" t="s">
+      <c r="P77" t="s">
         <v>221</v>
-      </c>
-      <c r="P77" t="s">
-        <v>222</v>
       </c>
       <c r="R77" t="s">
         <v>29</v>
@@ -6511,10 +6481,10 @@
         <v>30</v>
       </c>
       <c r="T77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="V77" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="W77" t="s">
         <v>31</v>
@@ -6526,7 +6496,7 @@
         <v>76</v>
       </c>
       <c r="Z77" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6537,34 +6507,34 @@
         <v>24</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D78" t="s">
+        <v>559</v>
+      </c>
+      <c r="E78" t="s">
+        <v>560</v>
+      </c>
+      <c r="F78" t="s">
+        <v>42</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="N78" t="s">
         <v>225</v>
       </c>
-      <c r="D78" t="s">
-        <v>560</v>
-      </c>
-      <c r="E78" t="s">
-        <v>561</v>
-      </c>
-      <c r="F78" t="s">
-        <v>42</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="N78" t="s">
+      <c r="P78" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>29</v>
@@ -6573,10 +6543,10 @@
         <v>30</v>
       </c>
       <c r="T78" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V78" t="s">
         <v>228</v>
-      </c>
-      <c r="V78" t="s">
-        <v>229</v>
       </c>
       <c r="W78" t="s">
         <v>31</v>
@@ -6588,7 +6558,7 @@
         <v>76</v>
       </c>
       <c r="Z78" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6599,44 +6569,44 @@
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D79" t="s">
+        <v>564</v>
+      </c>
+      <c r="E79" t="s">
         <v>565</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" t="s">
         <v>566</v>
       </c>
-      <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" t="s">
+      <c r="J79" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="L79" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M79" t="s">
         <v>36</v>
       </c>
       <c r="T79" s="1"/>
       <c r="V79" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W79" t="s">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s">
         <v>84</v>
       </c>
-      <c r="X79" t="s">
-        <v>85</v>
-      </c>
       <c r="Y79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z79" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6647,44 +6617,44 @@
         <v>24</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D80" t="s">
+        <v>568</v>
+      </c>
+      <c r="E80" t="s">
         <v>569</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" t="s">
         <v>570</v>
       </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="I80" t="s">
-        <v>571</v>
-      </c>
       <c r="J80" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M80" t="s">
         <v>36</v>
       </c>
       <c r="T80" s="1"/>
       <c r="V80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W80" t="s">
+        <v>83</v>
+      </c>
+      <c r="X80" t="s">
         <v>84</v>
       </c>
-      <c r="X80" t="s">
-        <v>85</v>
-      </c>
       <c r="Y80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z80" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6695,34 +6665,34 @@
         <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D81" t="s">
+        <v>571</v>
+      </c>
+      <c r="E81" t="s">
+        <v>572</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" t="s">
+        <v>573</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M81" t="s">
+        <v>675</v>
+      </c>
+      <c r="N81" t="s">
         <v>234</v>
       </c>
-      <c r="D81" t="s">
-        <v>572</v>
-      </c>
-      <c r="E81" t="s">
-        <v>573</v>
-      </c>
-      <c r="F81" t="s">
-        <v>42</v>
-      </c>
-      <c r="I81" t="s">
-        <v>574</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M81" t="s">
-        <v>676</v>
-      </c>
-      <c r="N81" t="s">
+      <c r="P81" t="s">
         <v>235</v>
-      </c>
-      <c r="P81" t="s">
-        <v>236</v>
       </c>
       <c r="R81" t="s">
         <v>29</v>
@@ -6731,10 +6701,10 @@
         <v>30</v>
       </c>
       <c r="T81" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V81" t="s">
         <v>237</v>
-      </c>
-      <c r="V81" t="s">
-        <v>238</v>
       </c>
       <c r="W81" t="s">
         <v>31</v>
@@ -6746,7 +6716,7 @@
         <v>60</v>
       </c>
       <c r="Z81" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6757,44 +6727,44 @@
         <v>24</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D82" t="s">
+        <v>574</v>
+      </c>
+      <c r="E82" t="s">
         <v>575</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" t="s">
         <v>576</v>
       </c>
-      <c r="F82" t="s">
-        <v>42</v>
-      </c>
-      <c r="I82" t="s">
-        <v>577</v>
-      </c>
       <c r="J82" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M82" t="s">
         <v>36</v>
       </c>
       <c r="T82" s="1"/>
       <c r="V82" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W82" t="s">
+        <v>83</v>
+      </c>
+      <c r="X82" t="s">
         <v>84</v>
       </c>
-      <c r="X82" t="s">
-        <v>85</v>
-      </c>
       <c r="Y82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z82" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6805,25 +6775,25 @@
         <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D83" t="s">
+        <v>577</v>
+      </c>
+      <c r="E83" t="s">
         <v>578</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" t="s">
         <v>579</v>
       </c>
-      <c r="F83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" t="s">
-        <v>580</v>
-      </c>
       <c r="J83" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -6832,19 +6802,19 @@
       <c r="R83" s="1"/>
       <c r="T83" s="1"/>
       <c r="V83" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W83" t="s">
+        <v>83</v>
+      </c>
+      <c r="X83" t="s">
         <v>84</v>
       </c>
-      <c r="X83" t="s">
-        <v>85</v>
-      </c>
       <c r="Y83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z83" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6855,25 +6825,25 @@
         <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D84" t="s">
+        <v>580</v>
+      </c>
+      <c r="E84" t="s">
         <v>581</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" t="s">
         <v>582</v>
       </c>
-      <c r="F84" t="s">
-        <v>42</v>
-      </c>
-      <c r="I84" t="s">
-        <v>583</v>
-      </c>
       <c r="J84" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -6882,19 +6852,19 @@
       <c r="R84" s="1"/>
       <c r="T84" s="1"/>
       <c r="V84" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W84" t="s">
+        <v>83</v>
+      </c>
+      <c r="X84" t="s">
         <v>84</v>
       </c>
-      <c r="X84" t="s">
-        <v>85</v>
-      </c>
       <c r="Y84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z84" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6905,47 +6875,47 @@
         <v>24</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D85" t="s">
+        <v>583</v>
+      </c>
+      <c r="E85" t="s">
         <v>584</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
         <v>585</v>
       </c>
-      <c r="F85" t="s">
-        <v>42</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="J85" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="L85" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M85" t="s">
         <v>36</v>
       </c>
       <c r="T85" s="1"/>
       <c r="V85" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W85" t="s">
+        <v>83</v>
+      </c>
+      <c r="X85" t="s">
         <v>84</v>
       </c>
-      <c r="X85" t="s">
-        <v>85</v>
-      </c>
       <c r="Y85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z85" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6956,34 +6926,34 @@
         <v>24</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D86" t="s">
+        <v>588</v>
+      </c>
+      <c r="E86" t="s">
+        <v>589</v>
+      </c>
+      <c r="F86" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" t="s">
+        <v>585</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="N86" t="s">
         <v>246</v>
       </c>
-      <c r="D86" t="s">
-        <v>589</v>
-      </c>
-      <c r="E86" t="s">
-        <v>590</v>
-      </c>
-      <c r="F86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>586</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="P86" t="s">
         <v>247</v>
-      </c>
-      <c r="P86" t="s">
-        <v>248</v>
       </c>
       <c r="R86" t="s">
         <v>29</v>
@@ -6992,10 +6962,10 @@
         <v>30</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V86" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="W86" t="s">
         <v>31</v>
@@ -7007,7 +6977,7 @@
         <v>60</v>
       </c>
       <c r="Z86" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="87" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7018,31 +6988,31 @@
         <v>24</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D87" t="s">
+        <v>591</v>
+      </c>
+      <c r="E87" t="s">
+        <v>592</v>
+      </c>
+      <c r="F87" t="s">
+        <v>42</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D87" t="s">
-        <v>592</v>
-      </c>
-      <c r="E87" t="s">
-        <v>593</v>
-      </c>
-      <c r="F87" t="s">
-        <v>42</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="N87" s="1" t="s">
+      <c r="P87" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="P87" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>29</v>
@@ -7051,10 +7021,10 @@
         <v>30</v>
       </c>
       <c r="T87" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="V87" t="s">
         <v>253</v>
-      </c>
-      <c r="V87" t="s">
-        <v>254</v>
       </c>
       <c r="W87" t="s">
         <v>31</v>
@@ -7066,7 +7036,7 @@
         <v>76</v>
       </c>
       <c r="Z87" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="88" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7077,37 +7047,37 @@
         <v>24</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D88" t="s">
+        <v>594</v>
+      </c>
+      <c r="E88" t="s">
         <v>595</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
         <v>596</v>
       </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="J88" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="L88" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s">
+        <v>254</v>
+      </c>
+      <c r="N88" t="s">
         <v>255</v>
       </c>
-      <c r="N88" t="s">
+      <c r="P88" t="s">
         <v>256</v>
-      </c>
-      <c r="P88" t="s">
-        <v>257</v>
       </c>
       <c r="R88" t="s">
         <v>29</v>
@@ -7116,10 +7086,10 @@
         <v>30</v>
       </c>
       <c r="T88" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V88" t="s">
         <v>258</v>
-      </c>
-      <c r="V88" t="s">
-        <v>259</v>
       </c>
       <c r="W88" t="s">
         <v>31</v>
@@ -7131,7 +7101,7 @@
         <v>60</v>
       </c>
       <c r="Z88" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7142,41 +7112,41 @@
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D89" t="s">
         <v>260</v>
       </c>
-      <c r="D89" t="s">
-        <v>261</v>
-      </c>
       <c r="E89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F89" t="s">
         <v>42</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="M89" t="s">
         <v>36</v>
       </c>
       <c r="T89" s="1"/>
       <c r="V89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W89" t="s">
+        <v>83</v>
+      </c>
+      <c r="X89" t="s">
         <v>84</v>
       </c>
-      <c r="X89" t="s">
-        <v>85</v>
-      </c>
       <c r="Y89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z89" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7187,44 +7157,44 @@
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D90" t="s">
         <v>263</v>
       </c>
-      <c r="D90" t="s">
-        <v>264</v>
-      </c>
       <c r="E90" t="s">
+        <v>600</v>
+      </c>
+      <c r="F90" t="s">
+        <v>42</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="F90" t="s">
-        <v>42</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="L90" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M90" t="s">
         <v>36</v>
       </c>
       <c r="T90" s="1"/>
       <c r="V90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W90" t="s">
+        <v>83</v>
+      </c>
+      <c r="X90" t="s">
         <v>84</v>
       </c>
-      <c r="X90" t="s">
-        <v>85</v>
-      </c>
       <c r="Y90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7235,41 +7205,41 @@
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91" t="s">
         <v>266</v>
       </c>
-      <c r="D91" t="s">
-        <v>267</v>
-      </c>
       <c r="E91" t="s">
+        <v>603</v>
+      </c>
+      <c r="F91" t="s">
+        <v>42</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="F91" t="s">
-        <v>42</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="L91" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M91" t="s">
         <v>36</v>
       </c>
       <c r="T91" s="1"/>
       <c r="V91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W91" t="s">
+        <v>83</v>
+      </c>
+      <c r="X91" t="s">
         <v>84</v>
       </c>
-      <c r="X91" t="s">
-        <v>85</v>
-      </c>
       <c r="Y91" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z91" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7280,41 +7250,41 @@
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D92" t="s">
         <v>269</v>
       </c>
-      <c r="D92" t="s">
-        <v>270</v>
-      </c>
       <c r="E92" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M92" t="s">
         <v>36</v>
       </c>
       <c r="T92" s="1"/>
       <c r="V92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W92" t="s">
+        <v>83</v>
+      </c>
+      <c r="X92" t="s">
         <v>84</v>
       </c>
-      <c r="X92" t="s">
-        <v>85</v>
-      </c>
       <c r="Y92" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z92" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7325,41 +7295,41 @@
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93" t="s">
         <v>271</v>
       </c>
-      <c r="D93" t="s">
-        <v>272</v>
-      </c>
       <c r="E93" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M93" t="s">
         <v>36</v>
       </c>
       <c r="T93" s="1"/>
       <c r="V93" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W93" t="s">
+        <v>83</v>
+      </c>
+      <c r="X93" t="s">
         <v>84</v>
       </c>
-      <c r="X93" t="s">
-        <v>85</v>
-      </c>
       <c r="Y93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z93" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7370,41 +7340,41 @@
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D94" t="s">
+        <v>607</v>
+      </c>
+      <c r="E94" t="s">
         <v>608</v>
       </c>
-      <c r="E94" t="s">
-        <v>609</v>
-      </c>
       <c r="F94" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M94" t="s">
         <v>36</v>
       </c>
       <c r="T94" s="1"/>
       <c r="V94" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W94" t="s">
+        <v>83</v>
+      </c>
+      <c r="X94" t="s">
         <v>84</v>
       </c>
-      <c r="X94" t="s">
-        <v>85</v>
-      </c>
       <c r="Y94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z94" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7415,41 +7385,41 @@
         <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D95" t="s">
         <v>274</v>
       </c>
-      <c r="D95" t="s">
-        <v>275</v>
-      </c>
       <c r="E95" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M95" t="s">
         <v>36</v>
       </c>
       <c r="T95" s="1"/>
       <c r="V95" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W95" t="s">
+        <v>83</v>
+      </c>
+      <c r="X95" t="s">
         <v>84</v>
       </c>
-      <c r="X95" t="s">
-        <v>85</v>
-      </c>
       <c r="Y95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z95" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7460,41 +7430,41 @@
         <v>24</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
+        <v>610</v>
+      </c>
+      <c r="E96" t="s">
         <v>611</v>
       </c>
-      <c r="E96" t="s">
-        <v>612</v>
-      </c>
       <c r="F96" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M96" t="s">
         <v>36</v>
       </c>
       <c r="T96" s="1"/>
       <c r="V96" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W96" t="s">
+        <v>83</v>
+      </c>
+      <c r="X96" t="s">
         <v>84</v>
       </c>
-      <c r="X96" t="s">
-        <v>85</v>
-      </c>
       <c r="Y96" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z96" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7505,41 +7475,41 @@
         <v>24</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" t="s">
         <v>277</v>
       </c>
-      <c r="D97" t="s">
-        <v>278</v>
-      </c>
       <c r="E97" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M97" t="s">
         <v>36</v>
       </c>
       <c r="T97" s="1"/>
       <c r="V97" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W97" t="s">
+        <v>83</v>
+      </c>
+      <c r="X97" t="s">
         <v>84</v>
       </c>
-      <c r="X97" t="s">
-        <v>85</v>
-      </c>
       <c r="Y97" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z97" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7550,41 +7520,41 @@
         <v>24</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" t="s">
         <v>279</v>
       </c>
-      <c r="D98" t="s">
-        <v>280</v>
-      </c>
       <c r="E98" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F98" t="s">
         <v>42</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s">
         <v>36</v>
       </c>
       <c r="T98" s="1"/>
       <c r="V98" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W98" t="s">
+        <v>83</v>
+      </c>
+      <c r="X98" t="s">
         <v>84</v>
       </c>
-      <c r="X98" t="s">
-        <v>85</v>
-      </c>
       <c r="Y98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z98" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7595,41 +7565,41 @@
         <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D99" t="s">
         <v>281</v>
       </c>
-      <c r="D99" t="s">
-        <v>282</v>
-      </c>
       <c r="E99" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M99" t="s">
         <v>36</v>
       </c>
       <c r="T99" s="1"/>
       <c r="V99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W99" t="s">
+        <v>83</v>
+      </c>
+      <c r="X99" t="s">
         <v>84</v>
       </c>
-      <c r="X99" t="s">
-        <v>85</v>
-      </c>
       <c r="Y99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z99" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7640,41 +7610,41 @@
         <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D100" t="s">
         <v>283</v>
       </c>
-      <c r="D100" t="s">
-        <v>284</v>
-      </c>
       <c r="E100" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F100" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M100" t="s">
         <v>36</v>
       </c>
       <c r="T100" s="1"/>
       <c r="V100" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W100" t="s">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s">
         <v>84</v>
       </c>
-      <c r="X100" t="s">
-        <v>85</v>
-      </c>
       <c r="Y100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z100" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7685,41 +7655,41 @@
         <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
         <v>285</v>
       </c>
-      <c r="D101" t="s">
-        <v>286</v>
-      </c>
       <c r="E101" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F101" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M101" t="s">
         <v>36</v>
       </c>
       <c r="T101" s="1"/>
       <c r="V101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W101" t="s">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s">
         <v>84</v>
       </c>
-      <c r="X101" t="s">
-        <v>85</v>
-      </c>
       <c r="Y101" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z101" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7730,41 +7700,41 @@
         <v>24</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102" t="s">
         <v>287</v>
       </c>
-      <c r="D102" t="s">
-        <v>288</v>
-      </c>
       <c r="E102" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F102" t="s">
         <v>42</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M102" t="s">
         <v>36</v>
       </c>
       <c r="T102" s="1"/>
       <c r="V102" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W102" t="s">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s">
         <v>84</v>
       </c>
-      <c r="X102" t="s">
-        <v>85</v>
-      </c>
       <c r="Y102" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z102" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7775,41 +7745,41 @@
         <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D103" t="s">
         <v>289</v>
       </c>
-      <c r="D103" t="s">
-        <v>290</v>
-      </c>
       <c r="E103" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F103" t="s">
         <v>42</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s">
         <v>36</v>
       </c>
       <c r="T103" s="1"/>
       <c r="V103" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W103" t="s">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s">
         <v>84</v>
       </c>
-      <c r="X103" t="s">
-        <v>85</v>
-      </c>
       <c r="Y103" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z103" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7820,41 +7790,41 @@
         <v>24</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D104" t="s">
         <v>291</v>
       </c>
-      <c r="D104" t="s">
-        <v>292</v>
-      </c>
       <c r="E104" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M104" t="s">
         <v>36</v>
       </c>
       <c r="T104" s="1"/>
       <c r="V104" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W104" t="s">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s">
         <v>84</v>
       </c>
-      <c r="X104" t="s">
-        <v>85</v>
-      </c>
       <c r="Y104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z104" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7865,41 +7835,41 @@
         <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D105" t="s">
         <v>293</v>
       </c>
-      <c r="D105" t="s">
-        <v>294</v>
-      </c>
       <c r="E105" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F105" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M105" t="s">
         <v>36</v>
       </c>
       <c r="T105" s="1"/>
       <c r="V105" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W105" t="s">
+        <v>83</v>
+      </c>
+      <c r="X105" t="s">
         <v>84</v>
       </c>
-      <c r="X105" t="s">
-        <v>85</v>
-      </c>
       <c r="Y105" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z105" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7910,41 +7880,41 @@
         <v>24</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D106" t="s">
         <v>295</v>
       </c>
-      <c r="D106" t="s">
-        <v>296</v>
-      </c>
       <c r="E106" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s">
         <v>36</v>
       </c>
       <c r="T106" s="1"/>
       <c r="V106" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W106" t="s">
+        <v>83</v>
+      </c>
+      <c r="X106" t="s">
         <v>84</v>
       </c>
-      <c r="X106" t="s">
-        <v>85</v>
-      </c>
       <c r="Y106" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z106" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7955,41 +7925,41 @@
         <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D107" t="s">
         <v>297</v>
       </c>
-      <c r="D107" t="s">
-        <v>298</v>
-      </c>
       <c r="E107" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F107" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M107" t="s">
         <v>36</v>
       </c>
       <c r="T107" s="1"/>
       <c r="V107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W107" t="s">
+        <v>83</v>
+      </c>
+      <c r="X107" t="s">
         <v>84</v>
       </c>
-      <c r="X107" t="s">
-        <v>85</v>
-      </c>
       <c r="Y107" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z107" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8000,41 +7970,41 @@
         <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D108" t="s">
         <v>299</v>
       </c>
-      <c r="D108" t="s">
-        <v>300</v>
-      </c>
       <c r="E108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F108" t="s">
         <v>42</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s">
         <v>36</v>
       </c>
       <c r="T108" s="1"/>
       <c r="V108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W108" t="s">
+        <v>83</v>
+      </c>
+      <c r="X108" t="s">
         <v>84</v>
       </c>
-      <c r="X108" t="s">
-        <v>85</v>
-      </c>
       <c r="Y108" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z108" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8045,41 +8015,41 @@
         <v>24</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" t="s">
         <v>301</v>
       </c>
-      <c r="D109" t="s">
-        <v>302</v>
-      </c>
       <c r="E109" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F109" t="s">
         <v>42</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M109" t="s">
         <v>36</v>
       </c>
       <c r="T109" s="1"/>
       <c r="V109" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W109" t="s">
+        <v>83</v>
+      </c>
+      <c r="X109" t="s">
         <v>84</v>
       </c>
-      <c r="X109" t="s">
-        <v>85</v>
-      </c>
       <c r="Y109" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z109" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8090,41 +8060,41 @@
         <v>24</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D110" t="s">
+        <v>625</v>
+      </c>
+      <c r="E110" t="s">
         <v>626</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>42</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="L110" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M110" t="s">
         <v>36</v>
       </c>
       <c r="T110" s="1"/>
       <c r="V110" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W110" t="s">
+        <v>83</v>
+      </c>
+      <c r="X110" t="s">
         <v>84</v>
       </c>
-      <c r="X110" t="s">
-        <v>85</v>
-      </c>
       <c r="Y110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z110" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8135,31 +8105,31 @@
         <v>24</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D111" t="s">
         <v>304</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>628</v>
+      </c>
+      <c r="F111" t="s">
+        <v>42</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M111" t="s">
         <v>305</v>
       </c>
-      <c r="E111" t="s">
-        <v>629</v>
-      </c>
-      <c r="F111" t="s">
-        <v>42</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M111" t="s">
+      <c r="N111" t="s">
         <v>306</v>
       </c>
-      <c r="N111" t="s">
+      <c r="P111" t="s">
         <v>307</v>
-      </c>
-      <c r="P111" t="s">
-        <v>308</v>
       </c>
       <c r="R111" t="s">
         <v>29</v>
@@ -8168,22 +8138,22 @@
         <v>30</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V111" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="W111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X111" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z111" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8194,41 +8164,41 @@
         <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D112" t="s">
+        <v>630</v>
+      </c>
+      <c r="E112" t="s">
         <v>631</v>
       </c>
-      <c r="E112" t="s">
-        <v>632</v>
-      </c>
       <c r="F112" t="s">
         <v>42</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M112" t="s">
         <v>36</v>
       </c>
       <c r="T112" s="1"/>
       <c r="V112" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="W112" t="s">
+        <v>83</v>
+      </c>
+      <c r="X112" t="s">
         <v>84</v>
       </c>
-      <c r="X112" t="s">
-        <v>85</v>
-      </c>
       <c r="Y112" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z112" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="113" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8239,22 +8209,22 @@
         <v>24</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D113" t="s">
+        <v>632</v>
+      </c>
+      <c r="E113" t="s">
+        <v>632</v>
+      </c>
+      <c r="F113" t="s">
+        <v>42</v>
+      </c>
+      <c r="J113" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="E113" t="s">
-        <v>633</v>
-      </c>
-      <c r="F113" t="s">
-        <v>42</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="L113" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>36</v>
@@ -8262,19 +8232,19 @@
       <c r="P113" s="1"/>
       <c r="T113" s="1"/>
       <c r="V113" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="W113" t="s">
+        <v>83</v>
+      </c>
+      <c r="X113" t="s">
         <v>84</v>
       </c>
-      <c r="X113" t="s">
-        <v>85</v>
-      </c>
       <c r="Y113" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z113" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8285,31 +8255,31 @@
         <v>24</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F114" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N114" t="s">
+        <v>246</v>
+      </c>
+      <c r="P114" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="R114" t="s">
         <v>29</v>
@@ -8318,10 +8288,10 @@
         <v>30</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V114" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="W114" t="s">
         <v>31</v>
@@ -8333,7 +8303,7 @@
         <v>60</v>
       </c>
       <c r="Z114" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="115" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8344,22 +8314,22 @@
         <v>24</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F115" t="s">
         <v>42</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>36</v>
@@ -8367,19 +8337,19 @@
       <c r="P115" s="1"/>
       <c r="T115" s="1"/>
       <c r="V115" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W115" t="s">
+        <v>83</v>
+      </c>
+      <c r="X115" t="s">
         <v>84</v>
       </c>
-      <c r="X115" t="s">
-        <v>85</v>
-      </c>
       <c r="Y115" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z115" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8390,37 +8360,37 @@
         <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D116" t="s">
+        <v>635</v>
+      </c>
+      <c r="E116" t="s">
+        <v>635</v>
+      </c>
+      <c r="F116" t="s">
+        <v>42</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="E116" t="s">
-        <v>636</v>
-      </c>
-      <c r="F116" t="s">
-        <v>42</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="M116" t="s">
         <v>36</v>
       </c>
       <c r="V116" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W116" t="s">
+        <v>83</v>
+      </c>
+      <c r="X116" t="s">
         <v>84</v>
       </c>
-      <c r="X116" t="s">
-        <v>85</v>
-      </c>
       <c r="Y116" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z116" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8431,37 +8401,37 @@
         <v>24</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D117" t="s">
+        <v>637</v>
+      </c>
+      <c r="E117" t="s">
+        <v>637</v>
+      </c>
+      <c r="F117" t="s">
+        <v>42</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="E117" t="s">
-        <v>638</v>
-      </c>
-      <c r="F117" t="s">
-        <v>42</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="M117" t="s">
         <v>36</v>
       </c>
       <c r="V117" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W117" t="s">
+        <v>83</v>
+      </c>
+      <c r="X117" t="s">
         <v>84</v>
       </c>
-      <c r="X117" t="s">
-        <v>85</v>
-      </c>
       <c r="Y117" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z117" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8472,37 +8442,37 @@
         <v>24</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D118" t="s">
+        <v>639</v>
+      </c>
+      <c r="E118" t="s">
+        <v>639</v>
+      </c>
+      <c r="F118" t="s">
+        <v>42</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E118" t="s">
-        <v>640</v>
-      </c>
-      <c r="F118" t="s">
-        <v>42</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="M118" t="s">
         <v>36</v>
       </c>
       <c r="V118" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W118" t="s">
+        <v>83</v>
+      </c>
+      <c r="X118" t="s">
         <v>84</v>
       </c>
-      <c r="X118" t="s">
-        <v>85</v>
-      </c>
       <c r="Y118" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z118" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8513,37 +8483,37 @@
         <v>24</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D119" t="s">
+        <v>641</v>
+      </c>
+      <c r="E119" t="s">
+        <v>641</v>
+      </c>
+      <c r="F119" t="s">
+        <v>42</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E119" t="s">
-        <v>642</v>
-      </c>
-      <c r="F119" t="s">
-        <v>42</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="M119" t="s">
         <v>36</v>
       </c>
       <c r="V119" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W119" t="s">
+        <v>83</v>
+      </c>
+      <c r="X119" t="s">
         <v>84</v>
       </c>
-      <c r="X119" t="s">
-        <v>85</v>
-      </c>
       <c r="Y119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z119" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8554,37 +8524,37 @@
         <v>24</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D120" t="s">
+        <v>643</v>
+      </c>
+      <c r="E120" t="s">
+        <v>643</v>
+      </c>
+      <c r="F120" t="s">
+        <v>42</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="E120" t="s">
-        <v>644</v>
-      </c>
-      <c r="F120" t="s">
-        <v>42</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="M120" t="s">
         <v>36</v>
       </c>
       <c r="V120" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W120" t="s">
+        <v>83</v>
+      </c>
+      <c r="X120" t="s">
         <v>84</v>
       </c>
-      <c r="X120" t="s">
-        <v>85</v>
-      </c>
       <c r="Y120" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z120" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8595,38 +8565,38 @@
         <v>24</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D121" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E121" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F121" t="s">
         <v>42</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M121" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="1"/>
       <c r="V121" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W121" t="s">
+        <v>83</v>
+      </c>
+      <c r="X121" t="s">
         <v>84</v>
       </c>
-      <c r="X121" t="s">
-        <v>85</v>
-      </c>
       <c r="Y121" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z121" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8637,37 +8607,37 @@
         <v>24</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D122" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E122" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F122" t="s">
         <v>42</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M122" t="s">
         <v>36</v>
       </c>
       <c r="V122" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W122" t="s">
+        <v>83</v>
+      </c>
+      <c r="X122" t="s">
         <v>84</v>
       </c>
-      <c r="X122" t="s">
-        <v>85</v>
-      </c>
       <c r="Y122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z122" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-DSE.xlsx
+++ b/baseline/data_processing_elements-DSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0D3DF5-FB93-415E-8CF6-B50DAF1BA63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85D40D7-6043-47B8-84F8-60A98C84F376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="683">
   <si>
     <t>index</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Ethnicity - Caucasian/White</t>
+  </si>
+  <si>
+    <t>No race/ethnicity item collected. DOSES records only country of birth (Denmark vs other; MA1_A_S4 / MA1_B_S5), which is not equivalent to the DataSchema race-based ethnicity categories.</t>
   </si>
   <si>
     <t>impossible</t>
@@ -2730,13 +2733,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>9</v>
@@ -2784,7 +2787,7 @@
         <v>23</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2795,19 +2798,19 @@
         <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M2" t="s">
         <v>26</v>
@@ -2851,13 +2854,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
@@ -2872,7 +2875,7 @@
         <v>37</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="120" x14ac:dyDescent="0.25">
@@ -2889,13 +2892,13 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
@@ -2910,7 +2913,7 @@
         <v>37</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -2927,13 +2930,13 @@
         <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F5" t="s">
         <v>42</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M5" t="s">
         <v>36</v>
@@ -2962,7 +2965,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -2974,10 +2977,10 @@
         <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M6" t="s">
         <v>47</v>
@@ -3027,7 +3030,7 @@
         <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -3074,7 +3077,7 @@
         <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -3083,10 +3086,10 @@
         <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M8" t="s">
         <v>65</v>
@@ -3127,25 +3130,25 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
         <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M9" t="s">
         <v>72</v>
@@ -3178,7 +3181,7 @@
         <v>77</v>
       </c>
       <c r="AA9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3189,7 +3192,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
@@ -3201,13 +3204,13 @@
         <v>42</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M10" t="s">
         <v>72</v>
@@ -3240,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3257,37 +3260,40 @@
         <v>82</v>
       </c>
       <c r="E11" t="s">
+        <v>420</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>421</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
-        <v>420</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="M11" t="s">
         <v>36</v>
       </c>
+      <c r="V11" t="s">
+        <v>83</v>
+      </c>
       <c r="W11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3298,43 +3304,46 @@
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>424</v>
+      </c>
+      <c r="E12" t="s">
+        <v>425</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
+        <v>426</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" t="s">
+        <v>83</v>
+      </c>
+      <c r="W12" t="s">
+        <v>84</v>
+      </c>
+      <c r="X12" t="s">
         <v>85</v>
       </c>
-      <c r="D12" t="s">
-        <v>423</v>
-      </c>
-      <c r="E12" t="s">
-        <v>424</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
-        <v>425</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M12" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" t="s">
-        <v>83</v>
-      </c>
-      <c r="X12" t="s">
-        <v>84</v>
-      </c>
       <c r="Y12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3345,43 +3354,46 @@
         <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F13" t="s">
         <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M13" t="s">
         <v>36</v>
       </c>
+      <c r="V13" t="s">
+        <v>83</v>
+      </c>
       <c r="W13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3392,43 +3404,46 @@
         <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F14" t="s">
         <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
       </c>
+      <c r="V14" t="s">
+        <v>83</v>
+      </c>
       <c r="W14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3439,43 +3454,46 @@
         <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F15" t="s">
         <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
       </c>
+      <c r="V15" t="s">
+        <v>83</v>
+      </c>
       <c r="W15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3486,43 +3504,46 @@
         <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
         <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M16" t="s">
         <v>36</v>
       </c>
+      <c r="V16" t="s">
+        <v>83</v>
+      </c>
       <c r="W16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,43 +3554,46 @@
         <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F17" t="s">
         <v>42</v>
       </c>
       <c r="I17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
       </c>
+      <c r="V17" t="s">
+        <v>83</v>
+      </c>
       <c r="W17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3580,43 +3604,46 @@
         <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F18" t="s">
         <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
       </c>
+      <c r="V18" t="s">
+        <v>83</v>
+      </c>
       <c r="W18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3627,43 +3654,46 @@
         <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F19" t="s">
         <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
       </c>
+      <c r="V19" t="s">
+        <v>83</v>
+      </c>
       <c r="W19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z19" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,29 +3704,29 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F20" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M20" t="s">
         <v>36</v>
       </c>
       <c r="T20" s="1"/>
       <c r="V20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="W20" t="s">
         <v>31</v>
@@ -3708,7 +3738,7 @@
         <v>37</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3719,34 +3749,34 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R21" t="s">
         <v>29</v>
@@ -3756,10 +3786,10 @@
       </c>
       <c r="T21" s="1"/>
       <c r="U21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W21" t="s">
         <v>31</v>
@@ -3771,7 +3801,7 @@
         <v>51</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
@@ -3782,28 +3812,28 @@
         <v>24</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R22" t="s">
         <v>29</v>
@@ -3812,10 +3842,10 @@
         <v>68</v>
       </c>
       <c r="U22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="W22" t="s">
         <v>31</v>
@@ -3838,25 +3868,25 @@
         <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R23" t="s">
         <v>29</v>
@@ -3865,10 +3895,10 @@
         <v>30</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="W23" t="s">
         <v>31</v>
@@ -3880,7 +3910,7 @@
         <v>60</v>
       </c>
       <c r="Z23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3891,29 +3921,29 @@
         <v>24</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M24" t="s">
         <v>36</v>
       </c>
       <c r="T24" s="1"/>
       <c r="V24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="W24" t="s">
         <v>31</v>
@@ -3925,7 +3955,7 @@
         <v>37</v>
       </c>
       <c r="Z24" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="180" customHeight="1" x14ac:dyDescent="0.25">
@@ -3936,28 +3966,28 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F25" t="s">
         <v>42</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R25" t="s">
         <v>29</v>
@@ -3966,22 +3996,22 @@
         <v>30</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z25" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,43 +4022,43 @@
         <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E26" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F26" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M26" t="s">
         <v>36</v>
       </c>
       <c r="V26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4039,34 +4069,34 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D27" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R27" t="s">
         <v>29</v>
@@ -4075,7 +4105,7 @@
         <v>68</v>
       </c>
       <c r="U27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="W27" t="s">
         <v>31</v>
@@ -4087,7 +4117,7 @@
         <v>76</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4098,28 +4128,28 @@
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F28" t="s">
         <v>42</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R28" t="s">
         <v>29</v>
@@ -4128,7 +4158,7 @@
         <v>68</v>
       </c>
       <c r="U28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="W28" t="s">
         <v>31</v>
@@ -4140,7 +4170,7 @@
         <v>76</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4151,34 +4181,34 @@
         <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R29" t="s">
         <v>29</v>
@@ -4187,7 +4217,7 @@
         <v>68</v>
       </c>
       <c r="U29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W29" t="s">
         <v>31</v>
@@ -4199,7 +4229,7 @@
         <v>76</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4210,28 +4240,28 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R30" t="s">
         <v>29</v>
@@ -4240,7 +4270,7 @@
         <v>68</v>
       </c>
       <c r="U30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W30" t="s">
         <v>31</v>
@@ -4252,7 +4282,7 @@
         <v>76</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4263,34 +4293,34 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E31" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R31" t="s">
         <v>29</v>
@@ -4299,10 +4329,10 @@
         <v>68</v>
       </c>
       <c r="U31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="W31" t="s">
         <v>31</v>
@@ -4314,7 +4344,7 @@
         <v>76</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4325,43 +4355,43 @@
         <v>24</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M32" t="s">
         <v>36</v>
       </c>
       <c r="V32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z32" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4372,37 +4402,37 @@
         <v>24</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M33" t="s">
         <v>36</v>
       </c>
       <c r="V33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z33" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -4413,28 +4443,28 @@
         <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R34" t="s">
         <v>29</v>
@@ -4443,7 +4473,7 @@
         <v>68</v>
       </c>
       <c r="U34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W34" t="s">
         <v>31</v>
@@ -4466,25 +4496,25 @@
         <v>24</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E35" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F35" t="s">
         <v>42</v>
       </c>
       <c r="M35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R35" t="s">
         <v>29</v>
@@ -4493,10 +4523,10 @@
         <v>68</v>
       </c>
       <c r="U35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V35" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W35" t="s">
         <v>31</v>
@@ -4508,7 +4538,7 @@
         <v>51</v>
       </c>
       <c r="Z35" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4519,34 +4549,34 @@
         <v>24</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R36" t="s">
         <v>29</v>
@@ -4555,10 +4585,10 @@
         <v>68</v>
       </c>
       <c r="U36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V36" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="W36" t="s">
         <v>31</v>
@@ -4570,7 +4600,7 @@
         <v>51</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4581,34 +4611,34 @@
         <v>24</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
+        <v>485</v>
+      </c>
+      <c r="F37" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F37" t="s">
-        <v>110</v>
-      </c>
-      <c r="G37" t="s">
-        <v>155</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="R37" t="s">
         <v>29</v>
@@ -4617,10 +4647,10 @@
         <v>68</v>
       </c>
       <c r="U37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V37" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="W37" t="s">
         <v>31</v>
@@ -4632,7 +4662,7 @@
         <v>70</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4643,34 +4673,34 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R38" t="s">
         <v>29</v>
@@ -4679,10 +4709,10 @@
         <v>68</v>
       </c>
       <c r="U38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V38" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="W38" t="s">
         <v>31</v>
@@ -4694,7 +4724,7 @@
         <v>70</v>
       </c>
       <c r="Z38" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4705,44 +4735,44 @@
         <v>24</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M39" t="s">
         <v>36</v>
       </c>
       <c r="P39" s="1"/>
       <c r="V39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="W39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z39" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4753,37 +4783,37 @@
         <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E40" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F40" t="s">
         <v>42</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M40" t="s">
         <v>36</v>
       </c>
       <c r="V40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z40" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -4794,37 +4824,37 @@
         <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D41" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E41" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
+        <v>171</v>
+      </c>
+      <c r="M41" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" t="s">
         <v>170</v>
       </c>
-      <c r="M41" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" t="s">
-        <v>169</v>
-      </c>
       <c r="W41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z41" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
@@ -4835,37 +4865,37 @@
         <v>24</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D42" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E42" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M42" t="s">
         <v>36</v>
       </c>
       <c r="V42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
@@ -4876,37 +4906,37 @@
         <v>24</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M43" t="s">
         <v>36</v>
       </c>
       <c r="V43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z43" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
@@ -4917,37 +4947,37 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" t="s">
+        <v>496</v>
+      </c>
+      <c r="E44" t="s">
+        <v>496</v>
+      </c>
+      <c r="F44" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" t="s">
         <v>174</v>
       </c>
-      <c r="D44" t="s">
-        <v>495</v>
-      </c>
-      <c r="E44" t="s">
-        <v>495</v>
-      </c>
-      <c r="F44" t="s">
-        <v>110</v>
-      </c>
-      <c r="G44" t="s">
-        <v>173</v>
-      </c>
       <c r="M44" t="s">
         <v>36</v>
       </c>
       <c r="V44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
@@ -4958,37 +4988,37 @@
         <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E45" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M45" t="s">
         <v>36</v>
       </c>
       <c r="V45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z45" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="180" customHeight="1" x14ac:dyDescent="0.25">
@@ -4999,41 +5029,41 @@
         <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E46" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N46" s="1"/>
       <c r="V46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z46" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -5044,37 +5074,37 @@
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M47" t="s">
         <v>36</v>
       </c>
       <c r="V47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -5085,37 +5115,37 @@
         <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D48" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E48" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M48" t="s">
         <v>36</v>
       </c>
       <c r="V48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5126,43 +5156,43 @@
         <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D49" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E49" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F49" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M49" t="s">
         <v>36</v>
       </c>
       <c r="V49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z49" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5173,40 +5203,40 @@
         <v>24</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D50" t="s">
+        <v>504</v>
+      </c>
+      <c r="E50" t="s">
+        <v>504</v>
+      </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="M50" t="s">
+        <v>36</v>
+      </c>
+      <c r="V50" t="s">
         <v>182</v>
       </c>
-      <c r="D50" t="s">
-        <v>503</v>
-      </c>
-      <c r="E50" t="s">
-        <v>503</v>
-      </c>
-      <c r="F50" t="s">
-        <v>42</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="M50" t="s">
-        <v>36</v>
-      </c>
-      <c r="V50" t="s">
-        <v>181</v>
-      </c>
       <c r="W50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z50" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="45" x14ac:dyDescent="0.25">
@@ -5217,43 +5247,43 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E51" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M51" t="s">
         <v>36</v>
       </c>
       <c r="V51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z51" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -5264,44 +5294,44 @@
         <v>24</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D52" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E52" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F52" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M52" t="s">
         <v>36</v>
       </c>
       <c r="T52" s="1"/>
       <c r="V52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z52" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -5312,37 +5342,37 @@
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s">
         <v>36</v>
       </c>
       <c r="V53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z53" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5353,44 +5383,44 @@
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D54" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E54" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M54" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="1"/>
       <c r="V54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z54" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -5401,37 +5431,37 @@
         <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E55" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F55" t="s">
         <v>42</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M55" t="s">
         <v>36</v>
       </c>
       <c r="V55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="W55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z55" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="270" customHeight="1" x14ac:dyDescent="0.25">
@@ -5442,34 +5472,34 @@
         <v>24</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F56" t="s">
         <v>42</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M56" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R56" t="s">
         <v>29</v>
@@ -5478,10 +5508,10 @@
         <v>30</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="W56" t="s">
         <v>31</v>
@@ -5493,7 +5523,7 @@
         <v>76</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -5504,31 +5534,31 @@
         <v>24</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" t="s">
         <v>42</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M57" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R57" t="s">
         <v>29</v>
@@ -5537,10 +5567,10 @@
         <v>30</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="W57" t="s">
         <v>31</v>
@@ -5552,7 +5582,7 @@
         <v>76</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="240" customHeight="1" x14ac:dyDescent="0.25">
@@ -5563,43 +5593,43 @@
         <v>24</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D58" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E58" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M58" t="s">
         <v>36</v>
       </c>
       <c r="V58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="W58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z58" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -5610,19 +5640,19 @@
         <v>24</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s">
         <v>36</v>
@@ -5630,19 +5660,19 @@
       <c r="R59" s="1"/>
       <c r="T59" s="1"/>
       <c r="V59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="W59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z59" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="390" customHeight="1" x14ac:dyDescent="0.25">
@@ -5653,22 +5683,22 @@
         <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F60" t="s">
         <v>42</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M60" t="s">
         <v>36</v>
@@ -5676,19 +5706,19 @@
       <c r="R60" s="1"/>
       <c r="T60" s="1"/>
       <c r="V60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="W60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z60" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5699,22 +5729,22 @@
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D61" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E61" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F61" t="s">
         <v>42</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M61" t="s">
         <v>36</v>
@@ -5723,19 +5753,19 @@
       <c r="R61" s="1"/>
       <c r="T61" s="1"/>
       <c r="V61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W61" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X61" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z61" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5746,40 +5776,40 @@
         <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" t="s">
         <v>42</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M62" t="s">
         <v>36</v>
       </c>
       <c r="V62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X62" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5790,38 +5820,38 @@
         <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D63" t="s">
+        <v>531</v>
+      </c>
+      <c r="E63" t="s">
+        <v>531</v>
+      </c>
+      <c r="F63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="E63" t="s">
-        <v>530</v>
-      </c>
-      <c r="F63" t="s">
-        <v>42</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="M63" t="s">
         <v>36</v>
       </c>
       <c r="R63" s="1"/>
       <c r="V63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="150" customHeight="1" x14ac:dyDescent="0.25">
@@ -5832,37 +5862,37 @@
         <v>24</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D64" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E64" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F64" t="s">
         <v>42</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M64" t="s">
         <v>36</v>
       </c>
       <c r="V64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z64" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5873,38 +5903,38 @@
         <v>24</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D65" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E65" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F65" t="s">
         <v>42</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M65" t="s">
         <v>36</v>
       </c>
       <c r="R65" s="1"/>
       <c r="V65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z65" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -5915,40 +5945,40 @@
         <v>24</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" t="s">
+        <v>536</v>
+      </c>
+      <c r="E66" t="s">
+        <v>216</v>
+      </c>
+      <c r="F66" t="s">
+        <v>42</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="M66" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" t="s">
         <v>214</v>
       </c>
-      <c r="D66" t="s">
-        <v>535</v>
-      </c>
-      <c r="E66" t="s">
-        <v>215</v>
-      </c>
-      <c r="F66" t="s">
-        <v>42</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="M66" t="s">
-        <v>36</v>
-      </c>
-      <c r="V66" t="s">
-        <v>213</v>
-      </c>
       <c r="W66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z66" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -5959,40 +5989,40 @@
         <v>24</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D67" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F67" t="s">
         <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M67" t="s">
         <v>36</v>
       </c>
       <c r="V67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z67" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6003,22 +6033,22 @@
         <v>24</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D68" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E68" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M68" t="s">
         <v>36</v>
@@ -6027,19 +6057,19 @@
       <c r="P68" s="1"/>
       <c r="R68" s="1"/>
       <c r="V68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z68" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6050,19 +6080,19 @@
         <v>24</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E69" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F69" t="s">
         <v>42</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M69" t="s">
         <v>36</v>
@@ -6071,19 +6101,19 @@
       <c r="P69" s="1"/>
       <c r="R69" s="1"/>
       <c r="V69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="W69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z69" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -6094,31 +6124,31 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D70" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E70" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F70" t="s">
         <v>42</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N70" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P70" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R70" t="s">
         <v>29</v>
@@ -6127,22 +6157,22 @@
         <v>30</v>
       </c>
       <c r="T70" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V70" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="W70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z70" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:26" ht="225" customHeight="1" x14ac:dyDescent="0.25">
@@ -6153,40 +6183,40 @@
         <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D71" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E71" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F71" t="s">
         <v>42</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M71" t="s">
         <v>36</v>
       </c>
       <c r="V71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z71" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6197,34 +6227,34 @@
         <v>24</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F72" t="s">
         <v>42</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P72" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R72" t="s">
         <v>29</v>
@@ -6233,22 +6263,22 @@
         <v>30</v>
       </c>
       <c r="T72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="V72" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="W72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X72" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z72" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:26" ht="285" customHeight="1" x14ac:dyDescent="0.25">
@@ -6259,41 +6289,41 @@
         <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E73" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F73" t="s">
         <v>42</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M73" t="s">
         <v>36</v>
       </c>
       <c r="T73" s="1"/>
       <c r="V73" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="W73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z73" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6304,34 +6334,34 @@
         <v>24</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E74" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F74" t="s">
         <v>42</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R74" t="s">
         <v>29</v>
@@ -6340,10 +6370,10 @@
         <v>30</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="V74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W74" t="s">
         <v>31</v>
@@ -6355,7 +6385,7 @@
         <v>60</v>
       </c>
       <c r="Z74" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6366,37 +6396,37 @@
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D75" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E75" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F75" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z75" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:26" ht="270" customHeight="1" x14ac:dyDescent="0.25">
@@ -6407,37 +6437,37 @@
         <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D76" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E76" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F76" t="s">
         <v>42</v>
       </c>
       <c r="G76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z76" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:26" ht="390" customHeight="1" x14ac:dyDescent="0.25">
@@ -6448,31 +6478,31 @@
         <v>24</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D77" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E77" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R77" t="s">
         <v>29</v>
@@ -6481,10 +6511,10 @@
         <v>30</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="V77" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="W77" t="s">
         <v>31</v>
@@ -6496,7 +6526,7 @@
         <v>76</v>
       </c>
       <c r="Z77" s="7" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6507,34 +6537,34 @@
         <v>24</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E78" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F78" t="s">
         <v>42</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N78" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>29</v>
@@ -6543,10 +6573,10 @@
         <v>30</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="V78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="W78" t="s">
         <v>31</v>
@@ -6558,7 +6588,7 @@
         <v>76</v>
       </c>
       <c r="Z78" s="7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6569,44 +6599,44 @@
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D79" t="s">
+        <v>565</v>
+      </c>
+      <c r="E79" t="s">
+        <v>566</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" t="s">
+        <v>567</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="L79" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="E79" t="s">
-        <v>565</v>
-      </c>
-      <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" t="s">
-        <v>566</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="M79" t="s">
         <v>36</v>
       </c>
       <c r="T79" s="1"/>
       <c r="V79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="W79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z79" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6617,44 +6647,44 @@
         <v>24</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D80" t="s">
+        <v>569</v>
+      </c>
+      <c r="E80" t="s">
+        <v>570</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" t="s">
+        <v>571</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="E80" t="s">
-        <v>569</v>
-      </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="I80" t="s">
-        <v>570</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="L80" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M80" t="s">
         <v>36</v>
       </c>
       <c r="T80" s="1"/>
       <c r="V80" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="W80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z80" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6665,34 +6695,34 @@
         <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D81" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E81" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F81" t="s">
         <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M81" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N81" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P81" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R81" t="s">
         <v>29</v>
@@ -6701,10 +6731,10 @@
         <v>30</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="V81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="W81" t="s">
         <v>31</v>
@@ -6716,7 +6746,7 @@
         <v>60</v>
       </c>
       <c r="Z81" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6727,44 +6757,44 @@
         <v>24</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D82" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E82" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F82" t="s">
         <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M82" t="s">
         <v>36</v>
       </c>
       <c r="T82" s="1"/>
       <c r="V82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="W82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z82" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6775,25 +6805,25 @@
         <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D83" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E83" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F83" t="s">
         <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -6802,19 +6832,19 @@
       <c r="R83" s="1"/>
       <c r="T83" s="1"/>
       <c r="V83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z83" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6825,25 +6855,25 @@
         <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D84" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E84" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F84" t="s">
         <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -6852,19 +6882,19 @@
       <c r="R84" s="1"/>
       <c r="T84" s="1"/>
       <c r="V84" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z84" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6875,47 +6905,47 @@
         <v>24</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D85" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E85" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F85" t="s">
         <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M85" t="s">
         <v>36</v>
       </c>
       <c r="T85" s="1"/>
       <c r="V85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="W85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z85" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6926,34 +6956,34 @@
         <v>24</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D86" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E86" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F86" t="s">
         <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R86" t="s">
         <v>29</v>
@@ -6962,10 +6992,10 @@
         <v>30</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V86" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="W86" t="s">
         <v>31</v>
@@ -6977,7 +7007,7 @@
         <v>60</v>
       </c>
       <c r="Z86" s="7" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="87" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6988,31 +7018,31 @@
         <v>24</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E87" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F87" t="s">
         <v>42</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>29</v>
@@ -7021,10 +7051,10 @@
         <v>30</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W87" t="s">
         <v>31</v>
@@ -7036,7 +7066,7 @@
         <v>76</v>
       </c>
       <c r="Z87" s="7" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="88" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7047,37 +7077,37 @@
         <v>24</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D88" t="s">
+        <v>595</v>
+      </c>
+      <c r="E88" t="s">
+        <v>596</v>
+      </c>
+      <c r="F88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
+        <v>597</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="E88" t="s">
-        <v>595</v>
-      </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I88" t="s">
-        <v>596</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>593</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R88" t="s">
         <v>29</v>
@@ -7086,10 +7116,10 @@
         <v>30</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="V88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W88" t="s">
         <v>31</v>
@@ -7101,7 +7131,7 @@
         <v>60</v>
       </c>
       <c r="Z88" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7112,41 +7142,41 @@
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F89" t="s">
         <v>42</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M89" t="s">
         <v>36</v>
       </c>
       <c r="T89" s="1"/>
       <c r="V89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="W89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X89" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z89" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7157,44 +7187,44 @@
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D90" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F90" t="s">
         <v>42</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M90" t="s">
         <v>36</v>
       </c>
       <c r="T90" s="1"/>
       <c r="V90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7205,41 +7235,41 @@
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E91" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F91" t="s">
         <v>42</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M91" t="s">
         <v>36</v>
       </c>
       <c r="T91" s="1"/>
       <c r="V91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X91" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z91" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7250,41 +7280,41 @@
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E92" t="s">
+        <v>606</v>
+      </c>
+      <c r="F92" t="s">
+        <v>42</v>
+      </c>
+      <c r="J92" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="F92" t="s">
-        <v>42</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="L92" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M92" t="s">
         <v>36</v>
       </c>
       <c r="T92" s="1"/>
       <c r="V92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W92" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X92" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y92" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z92" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7295,41 +7325,41 @@
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E93" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M93" t="s">
         <v>36</v>
       </c>
       <c r="T93" s="1"/>
       <c r="V93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X93" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z93" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7340,41 +7370,41 @@
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D94" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E94" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F94" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M94" t="s">
         <v>36</v>
       </c>
       <c r="T94" s="1"/>
       <c r="V94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W94" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y94" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z94" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7385,41 +7415,41 @@
         <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E95" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M95" t="s">
         <v>36</v>
       </c>
       <c r="T95" s="1"/>
       <c r="V95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W95" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X95" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y95" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z95" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7430,41 +7460,41 @@
         <v>24</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D96" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E96" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F96" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s">
         <v>36</v>
       </c>
       <c r="T96" s="1"/>
       <c r="V96" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W96" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X96" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y96" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z96" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7475,41 +7505,41 @@
         <v>24</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E97" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M97" t="s">
         <v>36</v>
       </c>
       <c r="T97" s="1"/>
       <c r="V97" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W97" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X97" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y97" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z97" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7520,41 +7550,41 @@
         <v>24</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E98" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F98" t="s">
         <v>42</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M98" t="s">
         <v>36</v>
       </c>
       <c r="T98" s="1"/>
       <c r="V98" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W98" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X98" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y98" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z98" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7565,41 +7595,41 @@
         <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E99" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M99" t="s">
         <v>36</v>
       </c>
       <c r="T99" s="1"/>
       <c r="V99" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W99" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X99" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y99" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z99" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7610,41 +7640,41 @@
         <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D100" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E100" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F100" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M100" t="s">
         <v>36</v>
       </c>
       <c r="T100" s="1"/>
       <c r="V100" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X100" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z100" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7655,41 +7685,41 @@
         <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E101" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F101" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M101" t="s">
         <v>36</v>
       </c>
       <c r="T101" s="1"/>
       <c r="V101" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W101" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X101" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y101" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z101" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7700,41 +7730,41 @@
         <v>24</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D102" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E102" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F102" t="s">
         <v>42</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M102" t="s">
         <v>36</v>
       </c>
       <c r="T102" s="1"/>
       <c r="V102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X102" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z102" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7745,41 +7775,41 @@
         <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E103" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F103" t="s">
         <v>42</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M103" t="s">
         <v>36</v>
       </c>
       <c r="T103" s="1"/>
       <c r="V103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W103" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X103" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y103" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z103" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7790,41 +7820,41 @@
         <v>24</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D104" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E104" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M104" t="s">
         <v>36</v>
       </c>
       <c r="T104" s="1"/>
       <c r="V104" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W104" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X104" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y104" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z104" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7835,41 +7865,41 @@
         <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E105" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F105" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M105" t="s">
         <v>36</v>
       </c>
       <c r="T105" s="1"/>
       <c r="V105" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z105" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7880,41 +7910,41 @@
         <v>24</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D106" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E106" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M106" t="s">
         <v>36</v>
       </c>
       <c r="T106" s="1"/>
       <c r="V106" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X106" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z106" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7925,41 +7955,41 @@
         <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D107" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E107" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F107" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M107" t="s">
         <v>36</v>
       </c>
       <c r="T107" s="1"/>
       <c r="V107" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W107" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X107" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y107" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z107" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7970,41 +8000,41 @@
         <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D108" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E108" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F108" t="s">
         <v>42</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M108" t="s">
         <v>36</v>
       </c>
       <c r="T108" s="1"/>
       <c r="V108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W108" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X108" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y108" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z108" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8015,41 +8045,41 @@
         <v>24</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D109" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E109" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F109" t="s">
         <v>42</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M109" t="s">
         <v>36</v>
       </c>
       <c r="T109" s="1"/>
       <c r="V109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W109" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X109" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y109" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z109" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8060,41 +8090,41 @@
         <v>24</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D110" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E110" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F110" t="s">
         <v>42</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M110" t="s">
         <v>36</v>
       </c>
       <c r="T110" s="1"/>
       <c r="V110" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W110" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X110" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y110" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z110" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8105,31 +8135,31 @@
         <v>24</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D111" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E111" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F111" t="s">
         <v>42</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N111" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R111" t="s">
         <v>29</v>
@@ -8138,22 +8168,22 @@
         <v>30</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="V111" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="W111" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X111" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y111" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z111" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8164,41 +8194,41 @@
         <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D112" t="s">
+        <v>631</v>
+      </c>
+      <c r="E112" t="s">
+        <v>632</v>
+      </c>
+      <c r="F112" t="s">
+        <v>42</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="E112" t="s">
-        <v>631</v>
-      </c>
-      <c r="F112" t="s">
-        <v>42</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="L112" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M112" t="s">
         <v>36</v>
       </c>
       <c r="T112" s="1"/>
       <c r="V112" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="W112" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X112" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y112" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z112" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8209,22 +8239,22 @@
         <v>24</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D113" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E113" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F113" t="s">
         <v>42</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>36</v>
@@ -8232,19 +8262,19 @@
       <c r="P113" s="1"/>
       <c r="T113" s="1"/>
       <c r="V113" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W113" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y113" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z113" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8255,31 +8285,31 @@
         <v>24</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D114" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E114" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F114" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R114" t="s">
         <v>29</v>
@@ -8288,10 +8318,10 @@
         <v>30</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="W114" t="s">
         <v>31</v>
@@ -8303,7 +8333,7 @@
         <v>60</v>
       </c>
       <c r="Z114" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8314,22 +8344,22 @@
         <v>24</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D115" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E115" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F115" t="s">
         <v>42</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>36</v>
@@ -8337,19 +8367,19 @@
       <c r="P115" s="1"/>
       <c r="T115" s="1"/>
       <c r="V115" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="W115" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X115" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y115" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z115" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8360,37 +8390,37 @@
         <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D116" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E116" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F116" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M116" t="s">
         <v>36</v>
       </c>
       <c r="V116" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W116" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X116" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y116" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z116" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="117" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8401,37 +8431,37 @@
         <v>24</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D117" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E117" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F117" t="s">
         <v>42</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M117" t="s">
         <v>36</v>
       </c>
       <c r="V117" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W117" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X117" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y117" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z117" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8442,37 +8472,37 @@
         <v>24</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E118" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F118" t="s">
         <v>42</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M118" t="s">
         <v>36</v>
       </c>
       <c r="V118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W118" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X118" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y118" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z118" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="119" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8483,37 +8513,37 @@
         <v>24</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D119" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E119" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F119" t="s">
         <v>42</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M119" t="s">
         <v>36</v>
       </c>
       <c r="V119" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W119" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X119" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y119" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z119" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8524,37 +8554,37 @@
         <v>24</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D120" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E120" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F120" t="s">
         <v>42</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M120" t="s">
         <v>36</v>
       </c>
       <c r="V120" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W120" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X120" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y120" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z120" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="121" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8565,38 +8595,38 @@
         <v>24</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D121" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E121" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F121" t="s">
         <v>42</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M121" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="1"/>
       <c r="V121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W121" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X121" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y121" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z121" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="122" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -8607,37 +8637,37 @@
         <v>24</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D122" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E122" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F122" t="s">
         <v>42</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M122" t="s">
         <v>36</v>
       </c>
       <c r="V122" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X122" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z122" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-DSE.xlsx
+++ b/baseline/data_processing_elements-DSE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\DPE_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85D40D7-6043-47B8-84F8-60A98C84F376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544A018F-912B-48FA-B526-1F3364AE180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,9 +504,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>MA1_T_S19</t>
-  </si>
-  <si>
     <t>MA1_T_S19: Body Fat Percentage</t>
   </si>
   <si>
@@ -2167,14 +2164,6 @@
 !is.na(MA1_T_BMI) ~ round(MA1_T_BMI, 2);
 is.na(MA1_T_BMI) &amp; !is.na(MA1_A_BMI) ~ round(MA1_A_BMI, 2);
 ELSE ~ NA_real_)</t>
-  </si>
-  <si>
-    <t>MA1_T_S17;
-MA1_A_S7</t>
-  </si>
-  <si>
-    <t>MA1_T_S16;
-MA1_A_S6</t>
   </si>
   <si>
     <t>case_when(
@@ -2257,6 +2246,17 @@
   </si>
   <si>
     <t>recode(1=1; 2=2; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>MA1_T_16;
+MA1_A_S6</t>
+  </si>
+  <si>
+    <t>MA1_T_17;
+MA1_A_S7</t>
+  </si>
+  <si>
+    <t>MA1_T_19</t>
   </si>
 </sst>
 </file>
@@ -2733,13 +2733,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>9</v>
@@ -2787,7 +2787,7 @@
         <v>23</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2798,19 +2798,19 @@
         <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E2" t="s">
         <v>399</v>
-      </c>
-      <c r="E2" t="s">
-        <v>400</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M2" t="s">
         <v>26</v>
@@ -2854,13 +2854,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
@@ -2875,7 +2875,7 @@
         <v>37</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="120" x14ac:dyDescent="0.25">
@@ -2892,13 +2892,13 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
@@ -2913,7 +2913,7 @@
         <v>37</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -2930,13 +2930,13 @@
         <v>41</v>
       </c>
       <c r="E5" t="s">
+        <v>405</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="M5" t="s">
         <v>36</v>
@@ -2965,7 +2965,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -2977,10 +2977,10 @@
         <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="M6" t="s">
         <v>47</v>
@@ -3030,7 +3030,7 @@
         <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -3077,7 +3077,7 @@
         <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -3086,10 +3086,10 @@
         <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="M8" t="s">
         <v>65</v>
@@ -3130,25 +3130,25 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
         <v>71</v>
       </c>
       <c r="E9" t="s">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="M9" t="s">
         <v>72</v>
@@ -3181,7 +3181,7 @@
         <v>77</v>
       </c>
       <c r="AA9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3192,7 +3192,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
@@ -3204,13 +3204,13 @@
         <v>42</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M10" t="s">
         <v>72</v>
@@ -3243,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,22 +3260,22 @@
         <v>82</v>
       </c>
       <c r="E11" t="s">
+        <v>419</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
         <v>420</v>
       </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M11" t="s">
         <v>36</v>
@@ -3307,25 +3307,25 @@
         <v>86</v>
       </c>
       <c r="D12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" t="s">
         <v>424</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
         <v>425</v>
       </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M12" t="s">
         <v>36</v>
@@ -3360,22 +3360,22 @@
         <v>88</v>
       </c>
       <c r="E13" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
         <v>428</v>
       </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M13" t="s">
         <v>36</v>
@@ -3410,22 +3410,22 @@
         <v>90</v>
       </c>
       <c r="E14" t="s">
+        <v>430</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" t="s">
         <v>431</v>
       </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
@@ -3460,22 +3460,22 @@
         <v>92</v>
       </c>
       <c r="E15" t="s">
+        <v>433</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
         <v>434</v>
       </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
@@ -3510,22 +3510,22 @@
         <v>94</v>
       </c>
       <c r="E16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
         <v>437</v>
       </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M16" t="s">
         <v>36</v>
@@ -3560,22 +3560,22 @@
         <v>96</v>
       </c>
       <c r="E17" t="s">
+        <v>439</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
         <v>440</v>
       </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
@@ -3607,25 +3607,25 @@
         <v>97</v>
       </c>
       <c r="D18" t="s">
+        <v>442</v>
+      </c>
+      <c r="E18" t="s">
         <v>443</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" t="s">
         <v>444</v>
       </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
@@ -3657,25 +3657,25 @@
         <v>98</v>
       </c>
       <c r="D19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" t="s">
         <v>447</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
         <v>448</v>
       </c>
-      <c r="F19" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
@@ -3710,23 +3710,23 @@
         <v>100</v>
       </c>
       <c r="E20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="M20" t="s">
         <v>36</v>
       </c>
       <c r="T20" s="1"/>
       <c r="V20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W20" t="s">
         <v>31</v>
@@ -3761,13 +3761,13 @@
         <v>42</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="M21" t="s">
         <v>105</v>
@@ -3789,7 +3789,7 @@
         <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W21" t="s">
         <v>31</v>
@@ -3815,10 +3815,10 @@
         <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F22" t="s">
         <v>111</v>
@@ -3845,7 +3845,7 @@
         <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W22" t="s">
         <v>31</v>
@@ -3898,7 +3898,7 @@
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W23" t="s">
         <v>31</v>
@@ -3927,23 +3927,23 @@
         <v>122</v>
       </c>
       <c r="E24" t="s">
+        <v>458</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="M24" t="s">
         <v>36</v>
       </c>
       <c r="T24" s="1"/>
       <c r="V24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="W24" t="s">
         <v>31</v>
@@ -3972,13 +3972,13 @@
         <v>125</v>
       </c>
       <c r="E25" t="s">
+        <v>461</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="M25" t="s">
         <v>126</v>
@@ -4025,22 +4025,22 @@
         <v>132</v>
       </c>
       <c r="D26" t="s">
+        <v>463</v>
+      </c>
+      <c r="E26" t="s">
         <v>464</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="F26" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="M26" t="s">
         <v>36</v>
@@ -4069,10 +4069,10 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E27" t="s">
         <v>134</v>
@@ -4084,13 +4084,13 @@
         <v>135</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="N27" t="s">
         <v>136</v>
@@ -4117,7 +4117,7 @@
         <v>76</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,22 +4128,22 @@
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D28" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" t="s">
+        <v>471</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="E28" t="s">
-        <v>472</v>
-      </c>
-      <c r="F28" t="s">
-        <v>42</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="N28" t="s">
         <v>136</v>
@@ -4170,7 +4170,7 @@
         <v>76</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4181,10 +4181,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E29" t="s">
         <v>138</v>
@@ -4196,13 +4196,13 @@
         <v>139</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="M29" s="1" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="N29" t="s">
         <v>140</v>
@@ -4229,7 +4229,7 @@
         <v>76</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4240,22 +4240,22 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="N30" t="s">
         <v>140</v>
@@ -4282,7 +4282,7 @@
         <v>76</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4293,13 +4293,13 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D31" t="s">
+        <v>475</v>
+      </c>
+      <c r="E31" t="s">
         <v>476</v>
-      </c>
-      <c r="E31" t="s">
-        <v>477</v>
       </c>
       <c r="F31" t="s">
         <v>111</v>
@@ -4308,10 +4308,10 @@
         <v>142</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="M31" t="s">
         <v>143</v>
@@ -4344,7 +4344,7 @@
         <v>76</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4355,13 +4355,13 @@
         <v>24</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F32" t="s">
         <v>111</v>
@@ -4370,10 +4370,10 @@
         <v>135</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="M32" t="s">
         <v>36</v>
@@ -4402,19 +4402,19 @@
         <v>24</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M33" t="s">
         <v>36</v>
@@ -4443,13 +4443,13 @@
         <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D34" t="s">
         <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F34" t="s">
         <v>111</v>
@@ -4458,13 +4458,13 @@
         <v>151</v>
       </c>
       <c r="M34" t="s">
+        <v>682</v>
+      </c>
+      <c r="N34" t="s">
         <v>152</v>
       </c>
-      <c r="N34" t="s">
+      <c r="P34" t="s">
         <v>153</v>
-      </c>
-      <c r="P34" t="s">
-        <v>154</v>
       </c>
       <c r="R34" t="s">
         <v>29</v>
@@ -4496,25 +4496,25 @@
         <v>24</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F35" t="s">
         <v>42</v>
       </c>
       <c r="M35" t="s">
+        <v>682</v>
+      </c>
+      <c r="N35" t="s">
         <v>152</v>
       </c>
-      <c r="N35" t="s">
+      <c r="P35" t="s">
         <v>153</v>
-      </c>
-      <c r="P35" t="s">
-        <v>154</v>
       </c>
       <c r="R35" t="s">
         <v>29</v>
@@ -4526,7 +4526,7 @@
         <v>151</v>
       </c>
       <c r="V35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="W35" t="s">
         <v>31</v>
@@ -4538,7 +4538,7 @@
         <v>51</v>
       </c>
       <c r="Z35" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4549,34 +4549,34 @@
         <v>24</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F36" t="s">
         <v>111</v>
       </c>
       <c r="G36" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="N36" t="s">
         <v>156</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="P36" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="R36" t="s">
         <v>29</v>
@@ -4585,10 +4585,10 @@
         <v>68</v>
       </c>
       <c r="U36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W36" t="s">
         <v>31</v>
@@ -4600,7 +4600,7 @@
         <v>51</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4611,34 +4611,34 @@
         <v>24</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F37" t="s">
         <v>111</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="N37" t="s">
+        <v>159</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="R37" t="s">
         <v>29</v>
@@ -4647,10 +4647,10 @@
         <v>68</v>
       </c>
       <c r="U37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V37" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W37" t="s">
         <v>31</v>
@@ -4662,7 +4662,7 @@
         <v>70</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4673,34 +4673,34 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F38" t="s">
         <v>111</v>
       </c>
       <c r="G38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="N38" t="s">
         <v>163</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="P38" t="s">
         <v>164</v>
-      </c>
-      <c r="P38" t="s">
-        <v>165</v>
       </c>
       <c r="R38" t="s">
         <v>29</v>
@@ -4709,10 +4709,10 @@
         <v>68</v>
       </c>
       <c r="U38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V38" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W38" t="s">
         <v>31</v>
@@ -4724,7 +4724,7 @@
         <v>70</v>
       </c>
       <c r="Z38" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,32 +4735,32 @@
         <v>24</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D39" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E39" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F39" t="s">
         <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="M39" t="s">
         <v>36</v>
       </c>
       <c r="P39" s="1"/>
       <c r="V39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W39" t="s">
         <v>84</v>
@@ -4783,25 +4783,25 @@
         <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" t="s">
+        <v>490</v>
+      </c>
+      <c r="E40" t="s">
+        <v>491</v>
+      </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" t="s">
         <v>169</v>
-      </c>
-      <c r="D40" t="s">
-        <v>491</v>
-      </c>
-      <c r="E40" t="s">
-        <v>492</v>
-      </c>
-      <c r="F40" t="s">
-        <v>42</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="M40" t="s">
-        <v>36</v>
-      </c>
-      <c r="V40" t="s">
-        <v>170</v>
       </c>
       <c r="W40" t="s">
         <v>84</v>
@@ -4824,25 +4824,25 @@
         <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D41" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E41" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F41" t="s">
         <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M41" t="s">
         <v>36</v>
       </c>
       <c r="V41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W41" t="s">
         <v>84</v>
@@ -4865,25 +4865,25 @@
         <v>24</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
         <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s">
         <v>36</v>
       </c>
       <c r="V42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W42" t="s">
         <v>84</v>
@@ -4906,25 +4906,25 @@
         <v>24</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F43" t="s">
         <v>111</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M43" t="s">
         <v>36</v>
       </c>
       <c r="V43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W43" t="s">
         <v>84</v>
@@ -4947,25 +4947,25 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F44" t="s">
         <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M44" t="s">
         <v>36</v>
       </c>
       <c r="V44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W44" t="s">
         <v>84</v>
@@ -4988,25 +4988,25 @@
         <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E45" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F45" t="s">
         <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M45" t="s">
         <v>36</v>
       </c>
       <c r="V45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W45" t="s">
         <v>84</v>
@@ -5029,29 +5029,29 @@
         <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E46" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F46" t="s">
         <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N46" s="1"/>
       <c r="V46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W46" t="s">
         <v>84</v>
@@ -5074,25 +5074,25 @@
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F47" t="s">
         <v>111</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M47" t="s">
         <v>36</v>
       </c>
       <c r="V47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W47" t="s">
         <v>84</v>
@@ -5115,25 +5115,25 @@
         <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F48" t="s">
         <v>111</v>
       </c>
       <c r="G48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M48" t="s">
         <v>36</v>
       </c>
       <c r="V48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W48" t="s">
         <v>84</v>
@@ -5156,31 +5156,31 @@
         <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E49" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F49" t="s">
         <v>111</v>
       </c>
       <c r="G49" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" t="s">
         <v>181</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M49" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" t="s">
-        <v>182</v>
       </c>
       <c r="W49" t="s">
         <v>84</v>
@@ -5203,28 +5203,28 @@
         <v>24</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D50" t="s">
+        <v>503</v>
+      </c>
+      <c r="E50" t="s">
+        <v>503</v>
+      </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E50" t="s">
-        <v>504</v>
-      </c>
-      <c r="F50" t="s">
-        <v>42</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="M50" t="s">
         <v>36</v>
       </c>
       <c r="V50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W50" t="s">
         <v>84</v>
@@ -5247,31 +5247,31 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D51" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E51" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F51" t="s">
         <v>111</v>
       </c>
       <c r="G51" t="s">
+        <v>180</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="M51" t="s">
+        <v>36</v>
+      </c>
+      <c r="V51" t="s">
         <v>181</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="M51" t="s">
-        <v>36</v>
-      </c>
-      <c r="V51" t="s">
-        <v>182</v>
       </c>
       <c r="W51" t="s">
         <v>84</v>
@@ -5294,32 +5294,32 @@
         <v>24</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D52" t="s">
+        <v>509</v>
+      </c>
+      <c r="E52" t="s">
+        <v>509</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E52" t="s">
-        <v>510</v>
-      </c>
-      <c r="F52" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="L52" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M52" t="s">
         <v>36</v>
       </c>
       <c r="T52" s="1"/>
       <c r="V52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W52" t="s">
         <v>84</v>
@@ -5342,25 +5342,25 @@
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F53" t="s">
         <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M53" t="s">
         <v>36</v>
       </c>
       <c r="V53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W53" t="s">
         <v>84</v>
@@ -5383,32 +5383,32 @@
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D54" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E54" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F54" t="s">
         <v>111</v>
       </c>
       <c r="G54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J54" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="M54" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="1"/>
       <c r="V54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W54" t="s">
         <v>84</v>
@@ -5431,25 +5431,25 @@
         <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" t="s">
+        <v>515</v>
+      </c>
+      <c r="E55" t="s">
+        <v>515</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="M55" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" t="s">
         <v>191</v>
-      </c>
-      <c r="D55" t="s">
-        <v>516</v>
-      </c>
-      <c r="E55" t="s">
-        <v>516</v>
-      </c>
-      <c r="F55" t="s">
-        <v>42</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="M55" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55" t="s">
-        <v>192</v>
       </c>
       <c r="W55" t="s">
         <v>84</v>
@@ -5472,34 +5472,34 @@
         <v>24</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D56" t="s">
         <v>193</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>193</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="M56" t="s">
+        <v>665</v>
+      </c>
+      <c r="N56" t="s">
         <v>194</v>
       </c>
-      <c r="E56" t="s">
-        <v>194</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="M56" t="s">
-        <v>668</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="P56" t="s">
         <v>195</v>
-      </c>
-      <c r="P56" t="s">
-        <v>196</v>
       </c>
       <c r="R56" t="s">
         <v>29</v>
@@ -5508,10 +5508,10 @@
         <v>30</v>
       </c>
       <c r="T56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="V56" t="s">
         <v>197</v>
-      </c>
-      <c r="V56" t="s">
-        <v>198</v>
       </c>
       <c r="W56" t="s">
         <v>31</v>
@@ -5523,7 +5523,7 @@
         <v>76</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -5534,31 +5534,31 @@
         <v>24</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D57" t="s">
         <v>199</v>
       </c>
-      <c r="D57" t="s">
-        <v>200</v>
-      </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" t="s">
         <v>42</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M57" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="N57" t="s">
+        <v>194</v>
+      </c>
+      <c r="P57" t="s">
         <v>195</v>
-      </c>
-      <c r="P57" t="s">
-        <v>196</v>
       </c>
       <c r="R57" t="s">
         <v>29</v>
@@ -5567,10 +5567,10 @@
         <v>30</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="W57" t="s">
         <v>31</v>
@@ -5582,7 +5582,7 @@
         <v>76</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="240" customHeight="1" x14ac:dyDescent="0.25">
@@ -5593,31 +5593,31 @@
         <v>24</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F58" t="s">
         <v>111</v>
       </c>
       <c r="G58" t="s">
+        <v>202</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="M58" t="s">
+        <v>36</v>
+      </c>
+      <c r="V58" t="s">
         <v>203</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="M58" t="s">
-        <v>36</v>
-      </c>
-      <c r="V58" t="s">
-        <v>204</v>
       </c>
       <c r="W58" t="s">
         <v>84</v>
@@ -5640,13 +5640,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D59" t="s">
         <v>205</v>
       </c>
-      <c r="D59" t="s">
-        <v>206</v>
-      </c>
       <c r="E59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F59" t="s">
         <v>111</v>
@@ -5660,7 +5660,7 @@
       <c r="R59" s="1"/>
       <c r="T59" s="1"/>
       <c r="V59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W59" t="s">
         <v>84</v>
@@ -5683,22 +5683,22 @@
         <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" t="s">
         <v>208</v>
       </c>
-      <c r="D60" t="s">
-        <v>209</v>
-      </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F60" t="s">
         <v>42</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="M60" t="s">
         <v>36</v>
@@ -5706,7 +5706,7 @@
       <c r="R60" s="1"/>
       <c r="T60" s="1"/>
       <c r="V60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W60" t="s">
         <v>84</v>
@@ -5729,22 +5729,22 @@
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
+        <v>525</v>
+      </c>
+      <c r="E61" t="s">
         <v>526</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F61" t="s">
-        <v>42</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="M61" t="s">
         <v>36</v>
@@ -5753,7 +5753,7 @@
       <c r="R61" s="1"/>
       <c r="T61" s="1"/>
       <c r="V61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W61" t="s">
         <v>84</v>
@@ -5776,28 +5776,28 @@
         <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D62" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E62" t="s">
-        <v>212</v>
-      </c>
-      <c r="F62" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="L62" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M62" t="s">
+        <v>36</v>
+      </c>
+      <c r="V62" t="s">
         <v>213</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M62" t="s">
-        <v>36</v>
-      </c>
-      <c r="V62" t="s">
-        <v>214</v>
       </c>
       <c r="W62" t="s">
         <v>84</v>
@@ -5820,26 +5820,26 @@
         <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D63" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E63" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F63" t="s">
         <v>42</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M63" t="s">
         <v>36</v>
       </c>
       <c r="R63" s="1"/>
       <c r="V63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W63" t="s">
         <v>84</v>
@@ -5862,25 +5862,25 @@
         <v>24</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D64" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E64" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F64" t="s">
         <v>42</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M64" t="s">
         <v>36</v>
       </c>
       <c r="V64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W64" t="s">
         <v>84</v>
@@ -5903,26 +5903,26 @@
         <v>24</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D65" t="s">
+        <v>532</v>
+      </c>
+      <c r="E65" t="s">
         <v>533</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="F65" t="s">
-        <v>42</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="M65" t="s">
         <v>36</v>
       </c>
       <c r="R65" s="1"/>
       <c r="V65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W65" t="s">
         <v>84</v>
@@ -5945,28 +5945,28 @@
         <v>24</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>535</v>
+      </c>
+      <c r="E66" t="s">
         <v>215</v>
       </c>
-      <c r="D66" t="s">
-        <v>536</v>
-      </c>
-      <c r="E66" t="s">
-        <v>216</v>
-      </c>
       <c r="F66" t="s">
         <v>42</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M66" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" t="s">
         <v>213</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M66" t="s">
-        <v>36</v>
-      </c>
-      <c r="V66" t="s">
-        <v>214</v>
       </c>
       <c r="W66" t="s">
         <v>84</v>
@@ -5989,28 +5989,28 @@
         <v>24</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D67" t="s">
+        <v>536</v>
+      </c>
+      <c r="E67" t="s">
         <v>217</v>
       </c>
-      <c r="D67" t="s">
-        <v>537</v>
-      </c>
-      <c r="E67" t="s">
-        <v>218</v>
-      </c>
       <c r="F67" t="s">
         <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M67" t="s">
+        <v>36</v>
+      </c>
+      <c r="V67" t="s">
         <v>213</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M67" t="s">
-        <v>36</v>
-      </c>
-      <c r="V67" t="s">
-        <v>214</v>
       </c>
       <c r="W67" t="s">
         <v>84</v>
@@ -6033,13 +6033,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D68" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E68" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F68" t="s">
         <v>111</v>
@@ -6048,7 +6048,7 @@
         <v>112</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M68" t="s">
         <v>36</v>
@@ -6057,7 +6057,7 @@
       <c r="P68" s="1"/>
       <c r="R68" s="1"/>
       <c r="V68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W68" t="s">
         <v>84</v>
@@ -6080,19 +6080,19 @@
         <v>24</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E69" t="s">
+        <v>538</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="F69" t="s">
-        <v>42</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="M69" t="s">
         <v>36</v>
@@ -6101,7 +6101,7 @@
       <c r="P69" s="1"/>
       <c r="R69" s="1"/>
       <c r="V69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W69" t="s">
         <v>84</v>
@@ -6124,31 +6124,31 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D70" t="s">
+        <v>540</v>
+      </c>
+      <c r="E70" t="s">
         <v>541</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F70" t="s">
-        <v>42</v>
-      </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="M70" t="s">
+        <v>317</v>
+      </c>
+      <c r="N70" t="s">
         <v>318</v>
       </c>
-      <c r="N70" t="s">
+      <c r="P70" t="s">
         <v>319</v>
-      </c>
-      <c r="P70" t="s">
-        <v>320</v>
       </c>
       <c r="R70" t="s">
         <v>29</v>
@@ -6157,10 +6157,10 @@
         <v>30</v>
       </c>
       <c r="T70" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V70" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="W70" t="s">
         <v>84</v>
@@ -6183,28 +6183,28 @@
         <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D71" t="s">
+        <v>321</v>
+      </c>
+      <c r="E71" t="s">
         <v>322</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M71" t="s">
+        <v>36</v>
+      </c>
+      <c r="V71" t="s">
         <v>323</v>
-      </c>
-      <c r="F71" t="s">
-        <v>42</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="M71" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" t="s">
-        <v>324</v>
       </c>
       <c r="W71" t="s">
         <v>84</v>
@@ -6227,34 +6227,34 @@
         <v>24</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E72" t="s">
+        <v>545</v>
+      </c>
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M72" t="s">
         <v>325</v>
       </c>
-      <c r="E72" t="s">
-        <v>546</v>
-      </c>
-      <c r="F72" t="s">
-        <v>42</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>326</v>
       </c>
-      <c r="N72" t="s">
+      <c r="P72" t="s">
         <v>327</v>
-      </c>
-      <c r="P72" t="s">
-        <v>328</v>
       </c>
       <c r="R72" t="s">
         <v>29</v>
@@ -6263,10 +6263,10 @@
         <v>30</v>
       </c>
       <c r="T72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="V72" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="W72" t="s">
         <v>84</v>
@@ -6289,29 +6289,29 @@
         <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E73" t="s">
+        <v>547</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F73" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="L73" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s">
         <v>36</v>
       </c>
       <c r="T73" s="1"/>
       <c r="V73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="W73" t="s">
         <v>84</v>
@@ -6334,34 +6334,34 @@
         <v>24</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D74" t="s">
+        <v>332</v>
+      </c>
+      <c r="E74" t="s">
+        <v>549</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="M74" t="s">
         <v>333</v>
       </c>
-      <c r="E74" t="s">
-        <v>550</v>
-      </c>
-      <c r="F74" t="s">
-        <v>42</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>334</v>
       </c>
-      <c r="N74" t="s">
+      <c r="P74" t="s">
         <v>335</v>
-      </c>
-      <c r="P74" t="s">
-        <v>336</v>
       </c>
       <c r="R74" t="s">
         <v>29</v>
@@ -6370,10 +6370,10 @@
         <v>30</v>
       </c>
       <c r="T74" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="V74" t="s">
         <v>337</v>
-      </c>
-      <c r="V74" t="s">
-        <v>338</v>
       </c>
       <c r="W74" t="s">
         <v>31</v>
@@ -6385,7 +6385,7 @@
         <v>60</v>
       </c>
       <c r="Z74" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6396,25 +6396,25 @@
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D75" t="s">
+        <v>551</v>
+      </c>
+      <c r="E75" t="s">
         <v>552</v>
-      </c>
-      <c r="E75" t="s">
-        <v>553</v>
       </c>
       <c r="F75" t="s">
         <v>111</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="W75" t="s">
         <v>84</v>
@@ -6437,25 +6437,25 @@
         <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D76" t="s">
+        <v>554</v>
+      </c>
+      <c r="E76" t="s">
         <v>555</v>
       </c>
-      <c r="E76" t="s">
-        <v>556</v>
-      </c>
       <c r="F76" t="s">
         <v>42</v>
       </c>
       <c r="G76" t="s">
+        <v>339</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V76" t="s">
         <v>340</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V76" t="s">
-        <v>341</v>
       </c>
       <c r="W76" t="s">
         <v>84</v>
@@ -6478,31 +6478,31 @@
         <v>24</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" t="s">
+        <v>556</v>
+      </c>
+      <c r="E77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F77" t="s">
+        <v>42</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="N77" t="s">
         <v>220</v>
       </c>
-      <c r="D77" t="s">
-        <v>557</v>
-      </c>
-      <c r="E77" t="s">
-        <v>557</v>
-      </c>
-      <c r="F77" t="s">
-        <v>42</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="N77" t="s">
+      <c r="P77" t="s">
         <v>221</v>
-      </c>
-      <c r="P77" t="s">
-        <v>222</v>
       </c>
       <c r="R77" t="s">
         <v>29</v>
@@ -6511,10 +6511,10 @@
         <v>30</v>
       </c>
       <c r="T77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="V77" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="W77" t="s">
         <v>31</v>
@@ -6526,7 +6526,7 @@
         <v>76</v>
       </c>
       <c r="Z77" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6537,34 +6537,34 @@
         <v>24</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D78" t="s">
+        <v>559</v>
+      </c>
+      <c r="E78" t="s">
+        <v>560</v>
+      </c>
+      <c r="F78" t="s">
+        <v>42</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="N78" t="s">
         <v>225</v>
       </c>
-      <c r="D78" t="s">
-        <v>560</v>
-      </c>
-      <c r="E78" t="s">
-        <v>561</v>
-      </c>
-      <c r="F78" t="s">
-        <v>42</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="N78" t="s">
+      <c r="P78" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>29</v>
@@ -6573,10 +6573,10 @@
         <v>30</v>
       </c>
       <c r="T78" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V78" t="s">
         <v>228</v>
-      </c>
-      <c r="V78" t="s">
-        <v>229</v>
       </c>
       <c r="W78" t="s">
         <v>31</v>
@@ -6588,7 +6588,7 @@
         <v>76</v>
       </c>
       <c r="Z78" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6599,32 +6599,32 @@
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D79" t="s">
+        <v>564</v>
+      </c>
+      <c r="E79" t="s">
         <v>565</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" t="s">
         <v>566</v>
       </c>
-      <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" t="s">
+      <c r="J79" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="L79" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M79" t="s">
         <v>36</v>
       </c>
       <c r="T79" s="1"/>
       <c r="V79" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W79" t="s">
         <v>84</v>
@@ -6647,32 +6647,32 @@
         <v>24</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D80" t="s">
+        <v>568</v>
+      </c>
+      <c r="E80" t="s">
         <v>569</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" t="s">
         <v>570</v>
       </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="I80" t="s">
-        <v>571</v>
-      </c>
       <c r="J80" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M80" t="s">
         <v>36</v>
       </c>
       <c r="T80" s="1"/>
       <c r="V80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W80" t="s">
         <v>84</v>
@@ -6695,34 +6695,34 @@
         <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D81" t="s">
+        <v>571</v>
+      </c>
+      <c r="E81" t="s">
+        <v>572</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" t="s">
+        <v>573</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M81" t="s">
+        <v>673</v>
+      </c>
+      <c r="N81" t="s">
         <v>234</v>
       </c>
-      <c r="D81" t="s">
-        <v>572</v>
-      </c>
-      <c r="E81" t="s">
-        <v>573</v>
-      </c>
-      <c r="F81" t="s">
-        <v>42</v>
-      </c>
-      <c r="I81" t="s">
-        <v>574</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M81" t="s">
-        <v>676</v>
-      </c>
-      <c r="N81" t="s">
+      <c r="P81" t="s">
         <v>235</v>
-      </c>
-      <c r="P81" t="s">
-        <v>236</v>
       </c>
       <c r="R81" t="s">
         <v>29</v>
@@ -6731,10 +6731,10 @@
         <v>30</v>
       </c>
       <c r="T81" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V81" t="s">
         <v>237</v>
-      </c>
-      <c r="V81" t="s">
-        <v>238</v>
       </c>
       <c r="W81" t="s">
         <v>31</v>
@@ -6746,7 +6746,7 @@
         <v>60</v>
       </c>
       <c r="Z81" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6757,32 +6757,32 @@
         <v>24</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D82" t="s">
+        <v>574</v>
+      </c>
+      <c r="E82" t="s">
         <v>575</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" t="s">
         <v>576</v>
       </c>
-      <c r="F82" t="s">
-        <v>42</v>
-      </c>
-      <c r="I82" t="s">
-        <v>577</v>
-      </c>
       <c r="J82" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M82" t="s">
         <v>36</v>
       </c>
       <c r="T82" s="1"/>
       <c r="V82" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W82" t="s">
         <v>84</v>
@@ -6805,25 +6805,25 @@
         <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D83" t="s">
+        <v>577</v>
+      </c>
+      <c r="E83" t="s">
         <v>578</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" t="s">
         <v>579</v>
       </c>
-      <c r="F83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" t="s">
-        <v>580</v>
-      </c>
       <c r="J83" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -6832,7 +6832,7 @@
       <c r="R83" s="1"/>
       <c r="T83" s="1"/>
       <c r="V83" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W83" t="s">
         <v>84</v>
@@ -6855,25 +6855,25 @@
         <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D84" t="s">
+        <v>580</v>
+      </c>
+      <c r="E84" t="s">
         <v>581</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" t="s">
         <v>582</v>
       </c>
-      <c r="F84" t="s">
-        <v>42</v>
-      </c>
-      <c r="I84" t="s">
-        <v>583</v>
-      </c>
       <c r="J84" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -6882,7 +6882,7 @@
       <c r="R84" s="1"/>
       <c r="T84" s="1"/>
       <c r="V84" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W84" t="s">
         <v>84</v>
@@ -6905,35 +6905,35 @@
         <v>24</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D85" t="s">
+        <v>583</v>
+      </c>
+      <c r="E85" t="s">
         <v>584</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
         <v>585</v>
       </c>
-      <c r="F85" t="s">
-        <v>42</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="J85" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="L85" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M85" t="s">
         <v>36</v>
       </c>
       <c r="T85" s="1"/>
       <c r="V85" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W85" t="s">
         <v>84</v>
@@ -6956,34 +6956,34 @@
         <v>24</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D86" t="s">
+        <v>588</v>
+      </c>
+      <c r="E86" t="s">
+        <v>589</v>
+      </c>
+      <c r="F86" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" t="s">
+        <v>585</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="N86" t="s">
         <v>246</v>
       </c>
-      <c r="D86" t="s">
-        <v>589</v>
-      </c>
-      <c r="E86" t="s">
-        <v>590</v>
-      </c>
-      <c r="F86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>586</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="P86" t="s">
         <v>247</v>
-      </c>
-      <c r="P86" t="s">
-        <v>248</v>
       </c>
       <c r="R86" t="s">
         <v>29</v>
@@ -6992,10 +6992,10 @@
         <v>30</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V86" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="W86" t="s">
         <v>31</v>
@@ -7007,7 +7007,7 @@
         <v>60</v>
       </c>
       <c r="Z86" s="7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="87" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7018,31 +7018,31 @@
         <v>24</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D87" t="s">
+        <v>591</v>
+      </c>
+      <c r="E87" t="s">
+        <v>592</v>
+      </c>
+      <c r="F87" t="s">
+        <v>42</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D87" t="s">
-        <v>592</v>
-      </c>
-      <c r="E87" t="s">
-        <v>593</v>
-      </c>
-      <c r="F87" t="s">
-        <v>42</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="N87" s="1" t="s">
+      <c r="P87" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="P87" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>29</v>
@@ -7051,10 +7051,10 @@
         <v>30</v>
       </c>
       <c r="T87" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="V87" t="s">
         <v>253</v>
-      </c>
-      <c r="V87" t="s">
-        <v>254</v>
       </c>
       <c r="W87" t="s">
         <v>31</v>
@@ -7066,7 +7066,7 @@
         <v>76</v>
       </c>
       <c r="Z87" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="88" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7077,37 +7077,37 @@
         <v>24</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D88" t="s">
+        <v>594</v>
+      </c>
+      <c r="E88" t="s">
         <v>595</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
         <v>596</v>
       </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="J88" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="L88" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s">
+        <v>254</v>
+      </c>
+      <c r="N88" t="s">
         <v>255</v>
       </c>
-      <c r="N88" t="s">
+      <c r="P88" t="s">
         <v>256</v>
-      </c>
-      <c r="P88" t="s">
-        <v>257</v>
       </c>
       <c r="R88" t="s">
         <v>29</v>
@@ -7116,10 +7116,10 @@
         <v>30</v>
       </c>
       <c r="T88" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="V88" t="s">
         <v>258</v>
-      </c>
-      <c r="V88" t="s">
-        <v>259</v>
       </c>
       <c r="W88" t="s">
         <v>31</v>
@@ -7131,7 +7131,7 @@
         <v>60</v>
       </c>
       <c r="Z88" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7142,29 +7142,29 @@
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D89" t="s">
         <v>260</v>
       </c>
-      <c r="D89" t="s">
-        <v>261</v>
-      </c>
       <c r="E89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F89" t="s">
         <v>42</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="M89" t="s">
         <v>36</v>
       </c>
       <c r="T89" s="1"/>
       <c r="V89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W89" t="s">
         <v>84</v>
@@ -7187,32 +7187,32 @@
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D90" t="s">
         <v>263</v>
       </c>
-      <c r="D90" t="s">
-        <v>264</v>
-      </c>
       <c r="E90" t="s">
+        <v>600</v>
+      </c>
+      <c r="F90" t="s">
+        <v>42</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="F90" t="s">
-        <v>42</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="L90" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M90" t="s">
         <v>36</v>
       </c>
       <c r="T90" s="1"/>
       <c r="V90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W90" t="s">
         <v>84</v>
@@ -7235,29 +7235,29 @@
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91" t="s">
         <v>266</v>
       </c>
-      <c r="D91" t="s">
-        <v>267</v>
-      </c>
       <c r="E91" t="s">
+        <v>603</v>
+      </c>
+      <c r="F91" t="s">
+        <v>42</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="F91" t="s">
-        <v>42</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="L91" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M91" t="s">
         <v>36</v>
       </c>
       <c r="T91" s="1"/>
       <c r="V91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W91" t="s">
         <v>84</v>
@@ -7280,29 +7280,29 @@
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D92" t="s">
         <v>269</v>
       </c>
-      <c r="D92" t="s">
-        <v>270</v>
-      </c>
       <c r="E92" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M92" t="s">
         <v>36</v>
       </c>
       <c r="T92" s="1"/>
       <c r="V92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W92" t="s">
         <v>84</v>
@@ -7325,29 +7325,29 @@
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93" t="s">
         <v>271</v>
       </c>
-      <c r="D93" t="s">
-        <v>272</v>
-      </c>
       <c r="E93" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M93" t="s">
         <v>36</v>
       </c>
       <c r="T93" s="1"/>
       <c r="V93" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W93" t="s">
         <v>84</v>
@@ -7370,29 +7370,29 @@
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D94" t="s">
+        <v>607</v>
+      </c>
+      <c r="E94" t="s">
         <v>608</v>
       </c>
-      <c r="E94" t="s">
-        <v>609</v>
-      </c>
       <c r="F94" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M94" t="s">
         <v>36</v>
       </c>
       <c r="T94" s="1"/>
       <c r="V94" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W94" t="s">
         <v>84</v>
@@ -7415,29 +7415,29 @@
         <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D95" t="s">
         <v>274</v>
       </c>
-      <c r="D95" t="s">
-        <v>275</v>
-      </c>
       <c r="E95" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M95" t="s">
         <v>36</v>
       </c>
       <c r="T95" s="1"/>
       <c r="V95" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W95" t="s">
         <v>84</v>
@@ -7460,29 +7460,29 @@
         <v>24</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
+        <v>610</v>
+      </c>
+      <c r="E96" t="s">
         <v>611</v>
       </c>
-      <c r="E96" t="s">
-        <v>612</v>
-      </c>
       <c r="F96" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M96" t="s">
         <v>36</v>
       </c>
       <c r="T96" s="1"/>
       <c r="V96" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W96" t="s">
         <v>84</v>
@@ -7505,29 +7505,29 @@
         <v>24</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" t="s">
         <v>277</v>
       </c>
-      <c r="D97" t="s">
-        <v>278</v>
-      </c>
       <c r="E97" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M97" t="s">
         <v>36</v>
       </c>
       <c r="T97" s="1"/>
       <c r="V97" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W97" t="s">
         <v>84</v>
@@ -7550,29 +7550,29 @@
         <v>24</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" t="s">
         <v>279</v>
       </c>
-      <c r="D98" t="s">
-        <v>280</v>
-      </c>
       <c r="E98" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F98" t="s">
         <v>42</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s">
         <v>36</v>
       </c>
       <c r="T98" s="1"/>
       <c r="V98" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W98" t="s">
         <v>84</v>
@@ -7595,29 +7595,29 @@
         <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D99" t="s">
         <v>281</v>
       </c>
-      <c r="D99" t="s">
-        <v>282</v>
-      </c>
       <c r="E99" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M99" t="s">
         <v>36</v>
       </c>
       <c r="T99" s="1"/>
       <c r="V99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W99" t="s">
         <v>84</v>
@@ -7640,29 +7640,29 @@
         <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D100" t="s">
         <v>283</v>
       </c>
-      <c r="D100" t="s">
-        <v>284</v>
-      </c>
       <c r="E100" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F100" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M100" t="s">
         <v>36</v>
       </c>
       <c r="T100" s="1"/>
       <c r="V100" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W100" t="s">
         <v>84</v>
@@ -7685,29 +7685,29 @@
         <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
         <v>285</v>
       </c>
-      <c r="D101" t="s">
-        <v>286</v>
-      </c>
       <c r="E101" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F101" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M101" t="s">
         <v>36</v>
       </c>
       <c r="T101" s="1"/>
       <c r="V101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W101" t="s">
         <v>84</v>
@@ -7730,29 +7730,29 @@
         <v>24</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102" t="s">
         <v>287</v>
       </c>
-      <c r="D102" t="s">
-        <v>288</v>
-      </c>
       <c r="E102" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F102" t="s">
         <v>42</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M102" t="s">
         <v>36</v>
       </c>
       <c r="T102" s="1"/>
       <c r="V102" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W102" t="s">
         <v>84</v>
@@ -7775,29 +7775,29 @@
         <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D103" t="s">
         <v>289</v>
       </c>
-      <c r="D103" t="s">
-        <v>290</v>
-      </c>
       <c r="E103" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F103" t="s">
         <v>42</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s">
         <v>36</v>
       </c>
       <c r="T103" s="1"/>
       <c r="V103" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W103" t="s">
         <v>84</v>
@@ -7820,29 +7820,29 @@
         <v>24</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D104" t="s">
         <v>291</v>
       </c>
-      <c r="D104" t="s">
-        <v>292</v>
-      </c>
       <c r="E104" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M104" t="s">
         <v>36</v>
       </c>
       <c r="T104" s="1"/>
       <c r="V104" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W104" t="s">
         <v>84</v>
@@ -7865,29 +7865,29 @@
         <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D105" t="s">
         <v>293</v>
       </c>
-      <c r="D105" t="s">
-        <v>294</v>
-      </c>
       <c r="E105" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F105" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M105" t="s">
         <v>36</v>
       </c>
       <c r="T105" s="1"/>
       <c r="V105" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W105" t="s">
         <v>84</v>
@@ -7910,29 +7910,29 @@
         <v>24</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D106" t="s">
         <v>295</v>
       </c>
-      <c r="D106" t="s">
-        <v>296</v>
-      </c>
       <c r="E106" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s">
         <v>36</v>
       </c>
       <c r="T106" s="1"/>
       <c r="V106" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W106" t="s">
         <v>84</v>
@@ -7955,29 +7955,29 @@
         <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D107" t="s">
         <v>297</v>
       </c>
-      <c r="D107" t="s">
-        <v>298</v>
-      </c>
       <c r="E107" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F107" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M107" t="s">
         <v>36</v>
       </c>
       <c r="T107" s="1"/>
       <c r="V107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W107" t="s">
         <v>84</v>
@@ -8000,29 +8000,29 @@
         <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D108" t="s">
         <v>299</v>
       </c>
-      <c r="D108" t="s">
-        <v>300</v>
-      </c>
       <c r="E108" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F108" t="s">
         <v>42</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s">
         <v>36</v>
       </c>
       <c r="T108" s="1"/>
       <c r="V108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W108" t="s">
         <v>84</v>
@@ -8045,29 +8045,29 @@
         <v>24</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" t="s">
         <v>301</v>
       </c>
-      <c r="D109" t="s">
-        <v>302</v>
-      </c>
       <c r="E109" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F109" t="s">
         <v>42</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M109" t="s">
         <v>36</v>
       </c>
       <c r="T109" s="1"/>
       <c r="V109" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W109" t="s">
         <v>84</v>
@@ -8090,29 +8090,29 @@
         <v>24</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D110" t="s">
+        <v>625</v>
+      </c>
+      <c r="E110" t="s">
         <v>626</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>42</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="L110" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M110" t="s">
         <v>36</v>
       </c>
       <c r="T110" s="1"/>
       <c r="V110" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W110" t="s">
         <v>84</v>
@@ -8135,31 +8135,31 @@
         <v>24</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D111" t="s">
         <v>304</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>628</v>
+      </c>
+      <c r="F111" t="s">
+        <v>42</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="M111" t="s">
         <v>305</v>
       </c>
-      <c r="E111" t="s">
-        <v>629</v>
-      </c>
-      <c r="F111" t="s">
-        <v>42</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="M111" t="s">
+      <c r="N111" t="s">
         <v>306</v>
       </c>
-      <c r="N111" t="s">
+      <c r="P111" t="s">
         <v>307</v>
-      </c>
-      <c r="P111" t="s">
-        <v>308</v>
       </c>
       <c r="R111" t="s">
         <v>29</v>
@@ -8168,10 +8168,10 @@
         <v>30</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V111" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="W111" t="s">
         <v>84</v>
@@ -8194,29 +8194,29 @@
         <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D112" t="s">
+        <v>630</v>
+      </c>
+      <c r="E112" t="s">
         <v>631</v>
       </c>
-      <c r="E112" t="s">
-        <v>632</v>
-      </c>
       <c r="F112" t="s">
         <v>42</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M112" t="s">
         <v>36</v>
       </c>
       <c r="T112" s="1"/>
       <c r="V112" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="W112" t="s">
         <v>84</v>
@@ -8239,22 +8239,22 @@
         <v>24</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D113" t="s">
+        <v>632</v>
+      </c>
+      <c r="E113" t="s">
+        <v>632</v>
+      </c>
+      <c r="F113" t="s">
+        <v>42</v>
+      </c>
+      <c r="J113" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="E113" t="s">
-        <v>633</v>
-      </c>
-      <c r="F113" t="s">
-        <v>42</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="L113" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>36</v>
@@ -8262,7 +8262,7 @@
       <c r="P113" s="1"/>
       <c r="T113" s="1"/>
       <c r="V113" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="W113" t="s">
         <v>84</v>
@@ -8285,31 +8285,31 @@
         <v>24</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F114" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="N114" t="s">
+        <v>246</v>
+      </c>
+      <c r="P114" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="R114" t="s">
         <v>29</v>
@@ -8318,10 +8318,10 @@
         <v>30</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V114" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="W114" t="s">
         <v>31</v>
@@ -8333,7 +8333,7 @@
         <v>60</v>
       </c>
       <c r="Z114" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="115" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8344,22 +8344,22 @@
         <v>24</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F115" t="s">
         <v>42</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>36</v>
@@ -8367,7 +8367,7 @@
       <c r="P115" s="1"/>
       <c r="T115" s="1"/>
       <c r="V115" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W115" t="s">
         <v>84</v>
@@ -8390,25 +8390,25 @@
         <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D116" t="s">
+        <v>635</v>
+      </c>
+      <c r="E116" t="s">
+        <v>635</v>
+      </c>
+      <c r="F116" t="s">
+        <v>42</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="E116" t="s">
-        <v>636</v>
-      </c>
-      <c r="F116" t="s">
-        <v>42</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="M116" t="s">
         <v>36</v>
       </c>
       <c r="V116" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W116" t="s">
         <v>84</v>
@@ -8431,25 +8431,25 @@
         <v>24</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D117" t="s">
+        <v>637</v>
+      </c>
+      <c r="E117" t="s">
+        <v>637</v>
+      </c>
+      <c r="F117" t="s">
+        <v>42</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="E117" t="s">
-        <v>638</v>
-      </c>
-      <c r="F117" t="s">
-        <v>42</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="M117" t="s">
         <v>36</v>
       </c>
       <c r="V117" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W117" t="s">
         <v>84</v>
@@ -8472,25 +8472,25 @@
         <v>24</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D118" t="s">
+        <v>639</v>
+      </c>
+      <c r="E118" t="s">
+        <v>639</v>
+      </c>
+      <c r="F118" t="s">
+        <v>42</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E118" t="s">
-        <v>640</v>
-      </c>
-      <c r="F118" t="s">
-        <v>42</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="M118" t="s">
         <v>36</v>
       </c>
       <c r="V118" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W118" t="s">
         <v>84</v>
@@ -8513,25 +8513,25 @@
         <v>24</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D119" t="s">
+        <v>641</v>
+      </c>
+      <c r="E119" t="s">
+        <v>641</v>
+      </c>
+      <c r="F119" t="s">
+        <v>42</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E119" t="s">
-        <v>642</v>
-      </c>
-      <c r="F119" t="s">
-        <v>42</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="M119" t="s">
         <v>36</v>
       </c>
       <c r="V119" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W119" t="s">
         <v>84</v>
@@ -8554,25 +8554,25 @@
         <v>24</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D120" t="s">
+        <v>643</v>
+      </c>
+      <c r="E120" t="s">
+        <v>643</v>
+      </c>
+      <c r="F120" t="s">
+        <v>42</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="E120" t="s">
-        <v>644</v>
-      </c>
-      <c r="F120" t="s">
-        <v>42</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="M120" t="s">
         <v>36</v>
       </c>
       <c r="V120" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W120" t="s">
         <v>84</v>
@@ -8595,26 +8595,26 @@
         <v>24</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D121" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E121" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F121" t="s">
         <v>42</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M121" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="1"/>
       <c r="V121" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W121" t="s">
         <v>84</v>
@@ -8637,25 +8637,25 @@
         <v>24</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D122" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E122" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F122" t="s">
         <v>42</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M122" t="s">
         <v>36</v>
       </c>
       <c r="V122" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W122" t="s">
         <v>84</v>

--- a/baseline/data_processing_elements-DSE.xlsx
+++ b/baseline/data_processing_elements-DSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\DPE_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544A018F-912B-48FA-B526-1F3364AE180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FD2AD8-591E-4238-97AE-8549E610F6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -477,9 +477,6 @@
     <t>kg/m2</t>
   </si>
   <si>
-    <t>MA1_T_BMI</t>
-  </si>
-  <si>
     <t>MA1_T_BMI: Body mass index (BMI)(kg/m2)</t>
   </si>
   <si>
@@ -2104,9 +2101,6 @@
   </si>
   <si>
     <t>internal_comment</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(MA1_T_S19), "Bioelectrical impedance measurement (Tanita BC-418MA)", NA)</t>
   </si>
   <si>
     <t>round(rowMeans(select(.,MA1_T_Bpsys1,MA1_T_Bpsys2,MA1_T_Bpsys3), na.rm = TRUE), 2)</t>
@@ -2257,6 +2251,13 @@
   </si>
   <si>
     <t>MA1_T_19</t>
+  </si>
+  <si>
+    <t>MA1_T_BMI;
+MA1_A_BMI</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(MA1_T_19), "Bioelectrical impedance measurement (Tanita BC-418MA)", NA)</t>
   </si>
 </sst>
 </file>
@@ -2733,13 +2734,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>9</v>
@@ -2787,7 +2788,7 @@
         <v>23</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2798,19 +2799,19 @@
         <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E2" t="s">
         <v>398</v>
-      </c>
-      <c r="E2" t="s">
-        <v>399</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M2" t="s">
         <v>26</v>
@@ -2854,13 +2855,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
@@ -2875,7 +2876,7 @@
         <v>37</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="120" x14ac:dyDescent="0.25">
@@ -2892,13 +2893,13 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
@@ -2913,7 +2914,7 @@
         <v>37</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -2930,13 +2931,13 @@
         <v>41</v>
       </c>
       <c r="E5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="M5" t="s">
         <v>36</v>
@@ -2965,7 +2966,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -2977,10 +2978,10 @@
         <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="M6" t="s">
         <v>47</v>
@@ -3030,7 +3031,7 @@
         <v>42</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -3077,7 +3078,7 @@
         <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -3086,10 +3087,10 @@
         <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="M8" t="s">
         <v>65</v>
@@ -3130,25 +3131,25 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
         <v>71</v>
       </c>
       <c r="E9" t="s">
+        <v>413</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="M9" t="s">
         <v>72</v>
@@ -3181,7 +3182,7 @@
         <v>77</v>
       </c>
       <c r="AA9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3192,7 +3193,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
@@ -3204,13 +3205,13 @@
         <v>42</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M10" t="s">
         <v>72</v>
@@ -3243,7 +3244,7 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,22 +3261,22 @@
         <v>82</v>
       </c>
       <c r="E11" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
         <v>419</v>
       </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M11" t="s">
         <v>36</v>
@@ -3307,25 +3308,25 @@
         <v>86</v>
       </c>
       <c r="D12" t="s">
+        <v>422</v>
+      </c>
+      <c r="E12" t="s">
         <v>423</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
         <v>424</v>
       </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M12" t="s">
         <v>36</v>
@@ -3360,22 +3361,22 @@
         <v>88</v>
       </c>
       <c r="E13" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
         <v>427</v>
       </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M13" t="s">
         <v>36</v>
@@ -3410,22 +3411,22 @@
         <v>90</v>
       </c>
       <c r="E14" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" t="s">
         <v>430</v>
       </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
@@ -3460,22 +3461,22 @@
         <v>92</v>
       </c>
       <c r="E15" t="s">
+        <v>432</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
         <v>433</v>
       </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
@@ -3510,22 +3511,22 @@
         <v>94</v>
       </c>
       <c r="E16" t="s">
+        <v>435</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
         <v>436</v>
       </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M16" t="s">
         <v>36</v>
@@ -3560,22 +3561,22 @@
         <v>96</v>
       </c>
       <c r="E17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
         <v>439</v>
       </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
@@ -3607,25 +3608,25 @@
         <v>97</v>
       </c>
       <c r="D18" t="s">
+        <v>441</v>
+      </c>
+      <c r="E18" t="s">
         <v>442</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" t="s">
         <v>443</v>
       </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
@@ -3657,25 +3658,25 @@
         <v>98</v>
       </c>
       <c r="D19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E19" t="s">
         <v>446</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
         <v>447</v>
       </c>
-      <c r="F19" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
@@ -3710,23 +3711,23 @@
         <v>100</v>
       </c>
       <c r="E20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="M20" t="s">
         <v>36</v>
       </c>
       <c r="T20" s="1"/>
       <c r="V20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W20" t="s">
         <v>31</v>
@@ -3761,13 +3762,13 @@
         <v>42</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="M21" t="s">
         <v>105</v>
@@ -3789,7 +3790,7 @@
         <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W21" t="s">
         <v>31</v>
@@ -3815,10 +3816,10 @@
         <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F22" t="s">
         <v>111</v>
@@ -3845,7 +3846,7 @@
         <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W22" t="s">
         <v>31</v>
@@ -3898,7 +3899,7 @@
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W23" t="s">
         <v>31</v>
@@ -3927,23 +3928,23 @@
         <v>122</v>
       </c>
       <c r="E24" t="s">
+        <v>457</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="M24" t="s">
         <v>36</v>
       </c>
       <c r="T24" s="1"/>
       <c r="V24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W24" t="s">
         <v>31</v>
@@ -3972,13 +3973,13 @@
         <v>125</v>
       </c>
       <c r="E25" t="s">
+        <v>460</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="M25" t="s">
         <v>126</v>
@@ -4025,22 +4026,22 @@
         <v>132</v>
       </c>
       <c r="D26" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" t="s">
         <v>463</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F26" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="M26" t="s">
         <v>36</v>
@@ -4069,10 +4070,10 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D27" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E27" t="s">
         <v>134</v>
@@ -4084,13 +4085,13 @@
         <v>135</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N27" t="s">
         <v>136</v>
@@ -4117,7 +4118,7 @@
         <v>76</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,22 +4129,22 @@
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D28" t="s">
+        <v>470</v>
+      </c>
+      <c r="E28" t="s">
+        <v>470</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="E28" t="s">
-        <v>471</v>
-      </c>
-      <c r="F28" t="s">
-        <v>42</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N28" t="s">
         <v>136</v>
@@ -4170,7 +4171,7 @@
         <v>76</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4181,10 +4182,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E29" t="s">
         <v>138</v>
@@ -4196,13 +4197,13 @@
         <v>139</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="M29" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N29" t="s">
         <v>140</v>
@@ -4229,7 +4230,7 @@
         <v>76</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4240,22 +4241,22 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N30" t="s">
         <v>140</v>
@@ -4282,7 +4283,7 @@
         <v>76</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4293,13 +4294,13 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D31" t="s">
+        <v>474</v>
+      </c>
+      <c r="E31" t="s">
         <v>475</v>
-      </c>
-      <c r="E31" t="s">
-        <v>476</v>
       </c>
       <c r="F31" t="s">
         <v>111</v>
@@ -4308,19 +4309,19 @@
         <v>142</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="M31" t="s">
+      <c r="M31" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="N31" t="s">
         <v>143</v>
       </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>144</v>
-      </c>
-      <c r="P31" t="s">
-        <v>145</v>
       </c>
       <c r="R31" t="s">
         <v>29</v>
@@ -4329,10 +4330,10 @@
         <v>68</v>
       </c>
       <c r="U31" t="s">
+        <v>145</v>
+      </c>
+      <c r="V31" t="s">
         <v>146</v>
-      </c>
-      <c r="V31" t="s">
-        <v>147</v>
       </c>
       <c r="W31" t="s">
         <v>31</v>
@@ -4344,7 +4345,7 @@
         <v>76</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="60" x14ac:dyDescent="0.25">
@@ -4355,13 +4356,13 @@
         <v>24</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F32" t="s">
         <v>111</v>
@@ -4370,16 +4371,16 @@
         <v>135</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="M32" t="s">
         <v>36</v>
       </c>
       <c r="V32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W32" t="s">
         <v>84</v>
@@ -4402,25 +4403,25 @@
         <v>24</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M33" t="s">
         <v>36</v>
       </c>
       <c r="V33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W33" t="s">
         <v>84</v>
@@ -4443,28 +4444,28 @@
         <v>24</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E34" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F34" t="s">
         <v>111</v>
       </c>
       <c r="G34" t="s">
+        <v>150</v>
+      </c>
+      <c r="M34" t="s">
+        <v>680</v>
+      </c>
+      <c r="N34" t="s">
         <v>151</v>
       </c>
-      <c r="M34" t="s">
-        <v>682</v>
-      </c>
-      <c r="N34" t="s">
+      <c r="P34" t="s">
         <v>152</v>
-      </c>
-      <c r="P34" t="s">
-        <v>153</v>
       </c>
       <c r="R34" t="s">
         <v>29</v>
@@ -4473,7 +4474,7 @@
         <v>68</v>
       </c>
       <c r="U34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="W34" t="s">
         <v>31</v>
@@ -4496,25 +4497,25 @@
         <v>24</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D35" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E35" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F35" t="s">
         <v>42</v>
       </c>
       <c r="M35" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="N35" t="s">
+        <v>151</v>
+      </c>
+      <c r="P35" t="s">
         <v>152</v>
-      </c>
-      <c r="P35" t="s">
-        <v>153</v>
       </c>
       <c r="R35" t="s">
         <v>29</v>
@@ -4523,10 +4524,10 @@
         <v>68</v>
       </c>
       <c r="U35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="W35" t="s">
         <v>31</v>
@@ -4538,7 +4539,7 @@
         <v>51</v>
       </c>
       <c r="Z35" s="3" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4549,34 +4550,34 @@
         <v>24</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F36" t="s">
         <v>111</v>
       </c>
       <c r="G36" t="s">
+        <v>154</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="N36" t="s">
         <v>155</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="P36" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="R36" t="s">
         <v>29</v>
@@ -4585,10 +4586,10 @@
         <v>68</v>
       </c>
       <c r="U36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V36" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="W36" t="s">
         <v>31</v>
@@ -4600,7 +4601,7 @@
         <v>51</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4611,34 +4612,34 @@
         <v>24</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F37" t="s">
         <v>111</v>
       </c>
       <c r="G37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="N37" t="s">
+        <v>158</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="R37" t="s">
         <v>29</v>
@@ -4647,10 +4648,10 @@
         <v>68</v>
       </c>
       <c r="U37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V37" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="W37" t="s">
         <v>31</v>
@@ -4662,10 +4663,10 @@
         <v>70</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4673,34 +4674,34 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F38" t="s">
         <v>111</v>
       </c>
       <c r="G38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="N38" t="s">
         <v>162</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="P38" t="s">
         <v>163</v>
-      </c>
-      <c r="P38" t="s">
-        <v>164</v>
       </c>
       <c r="R38" t="s">
         <v>29</v>
@@ -4709,10 +4710,10 @@
         <v>68</v>
       </c>
       <c r="U38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V38" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="W38" t="s">
         <v>31</v>
@@ -4724,7 +4725,7 @@
         <v>70</v>
       </c>
       <c r="Z38" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,32 +4736,32 @@
         <v>24</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F39" t="s">
         <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="M39" t="s">
         <v>36</v>
       </c>
       <c r="P39" s="1"/>
       <c r="V39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W39" t="s">
         <v>84</v>
@@ -4783,25 +4784,25 @@
         <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E40" t="s">
+        <v>490</v>
+      </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" t="s">
         <v>168</v>
-      </c>
-      <c r="D40" t="s">
-        <v>490</v>
-      </c>
-      <c r="E40" t="s">
-        <v>491</v>
-      </c>
-      <c r="F40" t="s">
-        <v>42</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="M40" t="s">
-        <v>36</v>
-      </c>
-      <c r="V40" t="s">
-        <v>169</v>
       </c>
       <c r="W40" t="s">
         <v>84</v>
@@ -4824,25 +4825,25 @@
         <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F41" t="s">
         <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M41" t="s">
         <v>36</v>
       </c>
       <c r="V41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W41" t="s">
         <v>84</v>
@@ -4865,25 +4866,25 @@
         <v>24</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F42" t="s">
         <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M42" t="s">
         <v>36</v>
       </c>
       <c r="V42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W42" t="s">
         <v>84</v>
@@ -4906,25 +4907,25 @@
         <v>24</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F43" t="s">
         <v>111</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M43" t="s">
         <v>36</v>
       </c>
       <c r="V43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W43" t="s">
         <v>84</v>
@@ -4947,25 +4948,25 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E44" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F44" t="s">
         <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M44" t="s">
         <v>36</v>
       </c>
       <c r="V44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W44" t="s">
         <v>84</v>
@@ -4988,25 +4989,25 @@
         <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D45" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E45" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F45" t="s">
         <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M45" t="s">
         <v>36</v>
       </c>
       <c r="V45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W45" t="s">
         <v>84</v>
@@ -5029,29 +5030,29 @@
         <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F46" t="s">
         <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N46" s="1"/>
       <c r="V46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W46" t="s">
         <v>84</v>
@@ -5074,25 +5075,25 @@
         <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F47" t="s">
         <v>111</v>
       </c>
       <c r="G47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M47" t="s">
         <v>36</v>
       </c>
       <c r="V47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W47" t="s">
         <v>84</v>
@@ -5115,25 +5116,25 @@
         <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D48" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E48" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F48" t="s">
         <v>111</v>
       </c>
       <c r="G48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M48" t="s">
         <v>36</v>
       </c>
       <c r="V48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W48" t="s">
         <v>84</v>
@@ -5156,31 +5157,31 @@
         <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D49" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E49" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F49" t="s">
         <v>111</v>
       </c>
       <c r="G49" t="s">
+        <v>179</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" t="s">
         <v>180</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="M49" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" t="s">
-        <v>181</v>
       </c>
       <c r="W49" t="s">
         <v>84</v>
@@ -5203,28 +5204,28 @@
         <v>24</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D50" t="s">
+        <v>502</v>
+      </c>
+      <c r="E50" t="s">
+        <v>502</v>
+      </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E50" t="s">
-        <v>503</v>
-      </c>
-      <c r="F50" t="s">
-        <v>42</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="M50" t="s">
         <v>36</v>
       </c>
       <c r="V50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="W50" t="s">
         <v>84</v>
@@ -5247,31 +5248,31 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F51" t="s">
         <v>111</v>
       </c>
       <c r="G51" t="s">
+        <v>179</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="M51" t="s">
+        <v>36</v>
+      </c>
+      <c r="V51" t="s">
         <v>180</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="M51" t="s">
-        <v>36</v>
-      </c>
-      <c r="V51" t="s">
-        <v>181</v>
       </c>
       <c r="W51" t="s">
         <v>84</v>
@@ -5294,32 +5295,32 @@
         <v>24</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s">
+        <v>508</v>
+      </c>
+      <c r="E52" t="s">
+        <v>508</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E52" t="s">
-        <v>509</v>
-      </c>
-      <c r="F52" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="L52" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s">
         <v>36</v>
       </c>
       <c r="T52" s="1"/>
       <c r="V52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="W52" t="s">
         <v>84</v>
@@ -5342,25 +5343,25 @@
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F53" t="s">
         <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M53" t="s">
         <v>36</v>
       </c>
       <c r="V53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="W53" t="s">
         <v>84</v>
@@ -5383,32 +5384,32 @@
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D54" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E54" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F54" t="s">
         <v>111</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J54" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="M54" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="1"/>
       <c r="V54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W54" t="s">
         <v>84</v>
@@ -5431,25 +5432,25 @@
         <v>24</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" t="s">
+        <v>514</v>
+      </c>
+      <c r="E55" t="s">
+        <v>514</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M55" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" t="s">
         <v>190</v>
-      </c>
-      <c r="D55" t="s">
-        <v>515</v>
-      </c>
-      <c r="E55" t="s">
-        <v>515</v>
-      </c>
-      <c r="F55" t="s">
-        <v>42</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="M55" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55" t="s">
-        <v>191</v>
       </c>
       <c r="W55" t="s">
         <v>84</v>
@@ -5472,34 +5473,34 @@
         <v>24</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" t="s">
         <v>192</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>192</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="M56" t="s">
+        <v>663</v>
+      </c>
+      <c r="N56" t="s">
         <v>193</v>
       </c>
-      <c r="E56" t="s">
-        <v>193</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="M56" t="s">
-        <v>665</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="P56" t="s">
         <v>194</v>
-      </c>
-      <c r="P56" t="s">
-        <v>195</v>
       </c>
       <c r="R56" t="s">
         <v>29</v>
@@ -5508,10 +5509,10 @@
         <v>30</v>
       </c>
       <c r="T56" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="V56" t="s">
         <v>196</v>
-      </c>
-      <c r="V56" t="s">
-        <v>197</v>
       </c>
       <c r="W56" t="s">
         <v>31</v>
@@ -5523,7 +5524,7 @@
         <v>76</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -5534,31 +5535,31 @@
         <v>24</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" t="s">
         <v>198</v>
       </c>
-      <c r="D57" t="s">
-        <v>199</v>
-      </c>
       <c r="E57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" t="s">
         <v>42</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M57" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="N57" t="s">
+        <v>193</v>
+      </c>
+      <c r="P57" t="s">
         <v>194</v>
-      </c>
-      <c r="P57" t="s">
-        <v>195</v>
       </c>
       <c r="R57" t="s">
         <v>29</v>
@@ -5567,10 +5568,10 @@
         <v>30</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W57" t="s">
         <v>31</v>
@@ -5582,7 +5583,7 @@
         <v>76</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="240" customHeight="1" x14ac:dyDescent="0.25">
@@ -5593,31 +5594,31 @@
         <v>24</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F58" t="s">
         <v>111</v>
       </c>
       <c r="G58" t="s">
+        <v>201</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="M58" t="s">
+        <v>36</v>
+      </c>
+      <c r="V58" t="s">
         <v>202</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="M58" t="s">
-        <v>36</v>
-      </c>
-      <c r="V58" t="s">
-        <v>203</v>
       </c>
       <c r="W58" t="s">
         <v>84</v>
@@ -5640,13 +5641,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" t="s">
         <v>204</v>
       </c>
-      <c r="D59" t="s">
-        <v>205</v>
-      </c>
       <c r="E59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s">
         <v>111</v>
@@ -5660,7 +5661,7 @@
       <c r="R59" s="1"/>
       <c r="T59" s="1"/>
       <c r="V59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W59" t="s">
         <v>84</v>
@@ -5683,22 +5684,22 @@
         <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D60" t="s">
         <v>207</v>
       </c>
-      <c r="D60" t="s">
-        <v>208</v>
-      </c>
       <c r="E60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F60" t="s">
         <v>42</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="M60" t="s">
         <v>36</v>
@@ -5706,7 +5707,7 @@
       <c r="R60" s="1"/>
       <c r="T60" s="1"/>
       <c r="V60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W60" t="s">
         <v>84</v>
@@ -5729,22 +5730,22 @@
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D61" t="s">
+        <v>524</v>
+      </c>
+      <c r="E61" t="s">
         <v>525</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="F61" t="s">
-        <v>42</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>528</v>
       </c>
       <c r="M61" t="s">
         <v>36</v>
@@ -5753,7 +5754,7 @@
       <c r="R61" s="1"/>
       <c r="T61" s="1"/>
       <c r="V61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="W61" t="s">
         <v>84</v>
@@ -5776,28 +5777,28 @@
         <v>24</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D62" t="s">
+        <v>210</v>
+      </c>
+      <c r="E62" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E62" t="s">
-        <v>211</v>
-      </c>
-      <c r="F62" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="L62" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="M62" t="s">
+        <v>36</v>
+      </c>
+      <c r="V62" t="s">
         <v>212</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="M62" t="s">
-        <v>36</v>
-      </c>
-      <c r="V62" t="s">
-        <v>213</v>
       </c>
       <c r="W62" t="s">
         <v>84</v>
@@ -5820,26 +5821,26 @@
         <v>24</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D63" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E63" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F63" t="s">
         <v>42</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M63" t="s">
         <v>36</v>
       </c>
       <c r="R63" s="1"/>
       <c r="V63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W63" t="s">
         <v>84</v>
@@ -5862,25 +5863,25 @@
         <v>24</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D64" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E64" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F64" t="s">
         <v>42</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M64" t="s">
         <v>36</v>
       </c>
       <c r="V64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W64" t="s">
         <v>84</v>
@@ -5903,26 +5904,26 @@
         <v>24</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D65" t="s">
+        <v>531</v>
+      </c>
+      <c r="E65" t="s">
         <v>532</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="F65" t="s">
-        <v>42</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="M65" t="s">
         <v>36</v>
       </c>
       <c r="R65" s="1"/>
       <c r="V65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W65" t="s">
         <v>84</v>
@@ -5945,28 +5946,28 @@
         <v>24</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D66" t="s">
+        <v>534</v>
+      </c>
+      <c r="E66" t="s">
         <v>214</v>
       </c>
-      <c r="D66" t="s">
-        <v>535</v>
-      </c>
-      <c r="E66" t="s">
-        <v>215</v>
-      </c>
       <c r="F66" t="s">
         <v>42</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="M66" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" t="s">
         <v>212</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="M66" t="s">
-        <v>36</v>
-      </c>
-      <c r="V66" t="s">
-        <v>213</v>
       </c>
       <c r="W66" t="s">
         <v>84</v>
@@ -5989,28 +5990,28 @@
         <v>24</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" t="s">
+        <v>535</v>
+      </c>
+      <c r="E67" t="s">
         <v>216</v>
       </c>
-      <c r="D67" t="s">
-        <v>536</v>
-      </c>
-      <c r="E67" t="s">
-        <v>217</v>
-      </c>
       <c r="F67" t="s">
         <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="M67" t="s">
+        <v>36</v>
+      </c>
+      <c r="V67" t="s">
         <v>212</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="M67" t="s">
-        <v>36</v>
-      </c>
-      <c r="V67" t="s">
-        <v>213</v>
       </c>
       <c r="W67" t="s">
         <v>84</v>
@@ -6033,13 +6034,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D68" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E68" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F68" t="s">
         <v>111</v>
@@ -6048,7 +6049,7 @@
         <v>112</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M68" t="s">
         <v>36</v>
@@ -6057,7 +6058,7 @@
       <c r="P68" s="1"/>
       <c r="R68" s="1"/>
       <c r="V68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W68" t="s">
         <v>84</v>
@@ -6080,19 +6081,19 @@
         <v>24</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D69" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E69" t="s">
+        <v>537</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="F69" t="s">
-        <v>42</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="M69" t="s">
         <v>36</v>
@@ -6101,7 +6102,7 @@
       <c r="P69" s="1"/>
       <c r="R69" s="1"/>
       <c r="V69" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W69" t="s">
         <v>84</v>
@@ -6124,31 +6125,31 @@
         <v>24</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D70" t="s">
+        <v>539</v>
+      </c>
+      <c r="E70" t="s">
         <v>540</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="F70" t="s">
-        <v>42</v>
-      </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="M70" t="s">
+        <v>316</v>
+      </c>
+      <c r="N70" t="s">
         <v>317</v>
       </c>
-      <c r="N70" t="s">
+      <c r="P70" t="s">
         <v>318</v>
-      </c>
-      <c r="P70" t="s">
-        <v>319</v>
       </c>
       <c r="R70" t="s">
         <v>29</v>
@@ -6157,10 +6158,10 @@
         <v>30</v>
       </c>
       <c r="T70" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="V70" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="W70" t="s">
         <v>84</v>
@@ -6183,28 +6184,28 @@
         <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D71" t="s">
+        <v>320</v>
+      </c>
+      <c r="E71" t="s">
         <v>321</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="M71" t="s">
+        <v>36</v>
+      </c>
+      <c r="V71" t="s">
         <v>322</v>
-      </c>
-      <c r="F71" t="s">
-        <v>42</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M71" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" t="s">
-        <v>323</v>
       </c>
       <c r="W71" t="s">
         <v>84</v>
@@ -6227,34 +6228,34 @@
         <v>24</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D72" t="s">
+        <v>323</v>
+      </c>
+      <c r="E72" t="s">
+        <v>544</v>
+      </c>
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="M72" t="s">
         <v>324</v>
       </c>
-      <c r="E72" t="s">
-        <v>545</v>
-      </c>
-      <c r="F72" t="s">
-        <v>42</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>325</v>
       </c>
-      <c r="N72" t="s">
+      <c r="P72" t="s">
         <v>326</v>
-      </c>
-      <c r="P72" t="s">
-        <v>327</v>
       </c>
       <c r="R72" t="s">
         <v>29</v>
@@ -6263,10 +6264,10 @@
         <v>30</v>
       </c>
       <c r="T72" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="V72" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="W72" t="s">
         <v>84</v>
@@ -6289,29 +6290,29 @@
         <v>24</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E73" t="s">
+        <v>546</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F73" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="L73" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M73" t="s">
         <v>36</v>
       </c>
       <c r="T73" s="1"/>
       <c r="V73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="W73" t="s">
         <v>84</v>
@@ -6334,34 +6335,34 @@
         <v>24</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D74" t="s">
+        <v>331</v>
+      </c>
+      <c r="E74" t="s">
+        <v>548</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="M74" t="s">
         <v>332</v>
       </c>
-      <c r="E74" t="s">
-        <v>549</v>
-      </c>
-      <c r="F74" t="s">
-        <v>42</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>333</v>
       </c>
-      <c r="N74" t="s">
+      <c r="P74" t="s">
         <v>334</v>
-      </c>
-      <c r="P74" t="s">
-        <v>335</v>
       </c>
       <c r="R74" t="s">
         <v>29</v>
@@ -6370,10 +6371,10 @@
         <v>30</v>
       </c>
       <c r="T74" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="V74" t="s">
         <v>336</v>
-      </c>
-      <c r="V74" t="s">
-        <v>337</v>
       </c>
       <c r="W74" t="s">
         <v>31</v>
@@ -6385,7 +6386,7 @@
         <v>60</v>
       </c>
       <c r="Z74" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6396,25 +6397,25 @@
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D75" t="s">
+        <v>550</v>
+      </c>
+      <c r="E75" t="s">
         <v>551</v>
-      </c>
-      <c r="E75" t="s">
-        <v>552</v>
       </c>
       <c r="F75" t="s">
         <v>111</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="V75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="W75" t="s">
         <v>84</v>
@@ -6437,25 +6438,25 @@
         <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D76" t="s">
+        <v>553</v>
+      </c>
+      <c r="E76" t="s">
         <v>554</v>
       </c>
-      <c r="E76" t="s">
-        <v>555</v>
-      </c>
       <c r="F76" t="s">
         <v>42</v>
       </c>
       <c r="G76" t="s">
+        <v>338</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V76" t="s">
         <v>339</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V76" t="s">
-        <v>340</v>
       </c>
       <c r="W76" t="s">
         <v>84</v>
@@ -6478,31 +6479,31 @@
         <v>24</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D77" t="s">
+        <v>555</v>
+      </c>
+      <c r="E77" t="s">
+        <v>555</v>
+      </c>
+      <c r="F77" t="s">
+        <v>42</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="N77" t="s">
         <v>219</v>
       </c>
-      <c r="D77" t="s">
-        <v>556</v>
-      </c>
-      <c r="E77" t="s">
-        <v>556</v>
-      </c>
-      <c r="F77" t="s">
-        <v>42</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="N77" t="s">
+      <c r="P77" t="s">
         <v>220</v>
-      </c>
-      <c r="P77" t="s">
-        <v>221</v>
       </c>
       <c r="R77" t="s">
         <v>29</v>
@@ -6511,10 +6512,10 @@
         <v>30</v>
       </c>
       <c r="T77" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="V77" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="W77" t="s">
         <v>31</v>
@@ -6526,7 +6527,7 @@
         <v>76</v>
       </c>
       <c r="Z77" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6537,34 +6538,34 @@
         <v>24</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D78" t="s">
+        <v>558</v>
+      </c>
+      <c r="E78" t="s">
+        <v>559</v>
+      </c>
+      <c r="F78" t="s">
+        <v>42</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="N78" t="s">
         <v>224</v>
       </c>
-      <c r="D78" t="s">
-        <v>559</v>
-      </c>
-      <c r="E78" t="s">
-        <v>560</v>
-      </c>
-      <c r="F78" t="s">
-        <v>42</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="N78" t="s">
+      <c r="P78" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>29</v>
@@ -6573,10 +6574,10 @@
         <v>30</v>
       </c>
       <c r="T78" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="V78" t="s">
         <v>227</v>
-      </c>
-      <c r="V78" t="s">
-        <v>228</v>
       </c>
       <c r="W78" t="s">
         <v>31</v>
@@ -6588,7 +6589,7 @@
         <v>76</v>
       </c>
       <c r="Z78" s="7" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6599,32 +6600,32 @@
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D79" t="s">
+        <v>563</v>
+      </c>
+      <c r="E79" t="s">
         <v>564</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" t="s">
         <v>565</v>
       </c>
-      <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" t="s">
+      <c r="J79" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="L79" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M79" t="s">
         <v>36</v>
       </c>
       <c r="T79" s="1"/>
       <c r="V79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W79" t="s">
         <v>84</v>
@@ -6647,32 +6648,32 @@
         <v>24</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D80" t="s">
+        <v>567</v>
+      </c>
+      <c r="E80" t="s">
         <v>568</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" t="s">
         <v>569</v>
       </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="I80" t="s">
-        <v>570</v>
-      </c>
       <c r="J80" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M80" t="s">
         <v>36</v>
       </c>
       <c r="T80" s="1"/>
       <c r="V80" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W80" t="s">
         <v>84</v>
@@ -6695,34 +6696,34 @@
         <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D81" t="s">
+        <v>570</v>
+      </c>
+      <c r="E81" t="s">
+        <v>571</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" t="s">
+        <v>572</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="M81" t="s">
+        <v>671</v>
+      </c>
+      <c r="N81" t="s">
         <v>233</v>
       </c>
-      <c r="D81" t="s">
-        <v>571</v>
-      </c>
-      <c r="E81" t="s">
-        <v>572</v>
-      </c>
-      <c r="F81" t="s">
-        <v>42</v>
-      </c>
-      <c r="I81" t="s">
-        <v>573</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="M81" t="s">
-        <v>673</v>
-      </c>
-      <c r="N81" t="s">
+      <c r="P81" t="s">
         <v>234</v>
-      </c>
-      <c r="P81" t="s">
-        <v>235</v>
       </c>
       <c r="R81" t="s">
         <v>29</v>
@@ -6731,10 +6732,10 @@
         <v>30</v>
       </c>
       <c r="T81" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="V81" t="s">
         <v>236</v>
-      </c>
-      <c r="V81" t="s">
-        <v>237</v>
       </c>
       <c r="W81" t="s">
         <v>31</v>
@@ -6746,7 +6747,7 @@
         <v>60</v>
       </c>
       <c r="Z81" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6757,32 +6758,32 @@
         <v>24</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D82" t="s">
+        <v>573</v>
+      </c>
+      <c r="E82" t="s">
         <v>574</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" t="s">
         <v>575</v>
       </c>
-      <c r="F82" t="s">
-        <v>42</v>
-      </c>
-      <c r="I82" t="s">
-        <v>576</v>
-      </c>
       <c r="J82" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M82" t="s">
         <v>36</v>
       </c>
       <c r="T82" s="1"/>
       <c r="V82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="W82" t="s">
         <v>84</v>
@@ -6805,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D83" t="s">
+        <v>576</v>
+      </c>
+      <c r="E83" t="s">
         <v>577</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" t="s">
         <v>578</v>
       </c>
-      <c r="F83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" t="s">
-        <v>579</v>
-      </c>
       <c r="J83" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -6832,7 +6833,7 @@
       <c r="R83" s="1"/>
       <c r="T83" s="1"/>
       <c r="V83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W83" t="s">
         <v>84</v>
@@ -6855,25 +6856,25 @@
         <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D84" t="s">
+        <v>579</v>
+      </c>
+      <c r="E84" t="s">
         <v>580</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" t="s">
         <v>581</v>
       </c>
-      <c r="F84" t="s">
-        <v>42</v>
-      </c>
-      <c r="I84" t="s">
-        <v>582</v>
-      </c>
       <c r="J84" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -6882,7 +6883,7 @@
       <c r="R84" s="1"/>
       <c r="T84" s="1"/>
       <c r="V84" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W84" t="s">
         <v>84</v>
@@ -6905,35 +6906,35 @@
         <v>24</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D85" t="s">
+        <v>582</v>
+      </c>
+      <c r="E85" t="s">
         <v>583</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
         <v>584</v>
       </c>
-      <c r="F85" t="s">
-        <v>42</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="J85" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="L85" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M85" t="s">
         <v>36</v>
       </c>
       <c r="T85" s="1"/>
       <c r="V85" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W85" t="s">
         <v>84</v>
@@ -6956,34 +6957,34 @@
         <v>24</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" t="s">
+        <v>587</v>
+      </c>
+      <c r="E86" t="s">
+        <v>588</v>
+      </c>
+      <c r="F86" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" t="s">
+        <v>584</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="N86" t="s">
         <v>245</v>
       </c>
-      <c r="D86" t="s">
-        <v>588</v>
-      </c>
-      <c r="E86" t="s">
-        <v>589</v>
-      </c>
-      <c r="F86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>585</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="P86" t="s">
         <v>246</v>
-      </c>
-      <c r="P86" t="s">
-        <v>247</v>
       </c>
       <c r="R86" t="s">
         <v>29</v>
@@ -6992,10 +6993,10 @@
         <v>30</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V86" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="W86" t="s">
         <v>31</v>
@@ -7007,7 +7008,7 @@
         <v>60</v>
       </c>
       <c r="Z86" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="87" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7018,31 +7019,31 @@
         <v>24</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" t="s">
+        <v>590</v>
+      </c>
+      <c r="E87" t="s">
+        <v>591</v>
+      </c>
+      <c r="F87" t="s">
+        <v>42</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D87" t="s">
-        <v>591</v>
-      </c>
-      <c r="E87" t="s">
-        <v>592</v>
-      </c>
-      <c r="F87" t="s">
-        <v>42</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="N87" s="1" t="s">
+      <c r="P87" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="P87" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>29</v>
@@ -7051,10 +7052,10 @@
         <v>30</v>
       </c>
       <c r="T87" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="V87" t="s">
         <v>252</v>
-      </c>
-      <c r="V87" t="s">
-        <v>253</v>
       </c>
       <c r="W87" t="s">
         <v>31</v>
@@ -7066,7 +7067,7 @@
         <v>76</v>
       </c>
       <c r="Z87" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="88" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7077,37 +7078,37 @@
         <v>24</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D88" t="s">
+        <v>593</v>
+      </c>
+      <c r="E88" t="s">
         <v>594</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
         <v>595</v>
       </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="J88" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>597</v>
-      </c>
       <c r="L88" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M88" t="s">
+        <v>253</v>
+      </c>
+      <c r="N88" t="s">
         <v>254</v>
       </c>
-      <c r="N88" t="s">
+      <c r="P88" t="s">
         <v>255</v>
-      </c>
-      <c r="P88" t="s">
-        <v>256</v>
       </c>
       <c r="R88" t="s">
         <v>29</v>
@@ -7116,10 +7117,10 @@
         <v>30</v>
       </c>
       <c r="T88" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="V88" t="s">
         <v>257</v>
-      </c>
-      <c r="V88" t="s">
-        <v>258</v>
       </c>
       <c r="W88" t="s">
         <v>31</v>
@@ -7131,7 +7132,7 @@
         <v>60</v>
       </c>
       <c r="Z88" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7142,29 +7143,29 @@
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D89" t="s">
         <v>259</v>
       </c>
-      <c r="D89" t="s">
-        <v>260</v>
-      </c>
       <c r="E89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F89" t="s">
         <v>42</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="M89" t="s">
         <v>36</v>
       </c>
       <c r="T89" s="1"/>
       <c r="V89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="W89" t="s">
         <v>84</v>
@@ -7187,32 +7188,32 @@
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D90" t="s">
         <v>262</v>
       </c>
-      <c r="D90" t="s">
-        <v>263</v>
-      </c>
       <c r="E90" t="s">
+        <v>599</v>
+      </c>
+      <c r="F90" t="s">
+        <v>42</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="F90" t="s">
-        <v>42</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="L90" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M90" t="s">
         <v>36</v>
       </c>
       <c r="T90" s="1"/>
       <c r="V90" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W90" t="s">
         <v>84</v>
@@ -7235,29 +7236,29 @@
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D91" t="s">
         <v>265</v>
       </c>
-      <c r="D91" t="s">
-        <v>266</v>
-      </c>
       <c r="E91" t="s">
+        <v>602</v>
+      </c>
+      <c r="F91" t="s">
+        <v>42</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F91" t="s">
-        <v>42</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="L91" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M91" t="s">
         <v>36</v>
       </c>
       <c r="T91" s="1"/>
       <c r="V91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W91" t="s">
         <v>84</v>
@@ -7280,29 +7281,29 @@
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D92" t="s">
         <v>268</v>
       </c>
-      <c r="D92" t="s">
-        <v>269</v>
-      </c>
       <c r="E92" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M92" t="s">
         <v>36</v>
       </c>
       <c r="T92" s="1"/>
       <c r="V92" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W92" t="s">
         <v>84</v>
@@ -7325,29 +7326,29 @@
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" t="s">
         <v>270</v>
       </c>
-      <c r="D93" t="s">
-        <v>271</v>
-      </c>
       <c r="E93" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M93" t="s">
         <v>36</v>
       </c>
       <c r="T93" s="1"/>
       <c r="V93" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W93" t="s">
         <v>84</v>
@@ -7370,29 +7371,29 @@
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D94" t="s">
+        <v>606</v>
+      </c>
+      <c r="E94" t="s">
         <v>607</v>
       </c>
-      <c r="E94" t="s">
-        <v>608</v>
-      </c>
       <c r="F94" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M94" t="s">
         <v>36</v>
       </c>
       <c r="T94" s="1"/>
       <c r="V94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W94" t="s">
         <v>84</v>
@@ -7415,29 +7416,29 @@
         <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D95" t="s">
         <v>273</v>
       </c>
-      <c r="D95" t="s">
-        <v>274</v>
-      </c>
       <c r="E95" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M95" t="s">
         <v>36</v>
       </c>
       <c r="T95" s="1"/>
       <c r="V95" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W95" t="s">
         <v>84</v>
@@ -7460,29 +7461,29 @@
         <v>24</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D96" t="s">
+        <v>609</v>
+      </c>
+      <c r="E96" t="s">
         <v>610</v>
       </c>
-      <c r="E96" t="s">
-        <v>611</v>
-      </c>
       <c r="F96" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s">
         <v>36</v>
       </c>
       <c r="T96" s="1"/>
       <c r="V96" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W96" t="s">
         <v>84</v>
@@ -7505,29 +7506,29 @@
         <v>24</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D97" t="s">
         <v>276</v>
       </c>
-      <c r="D97" t="s">
-        <v>277</v>
-      </c>
       <c r="E97" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M97" t="s">
         <v>36</v>
       </c>
       <c r="T97" s="1"/>
       <c r="V97" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W97" t="s">
         <v>84</v>
@@ -7550,29 +7551,29 @@
         <v>24</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" t="s">
         <v>278</v>
       </c>
-      <c r="D98" t="s">
-        <v>279</v>
-      </c>
       <c r="E98" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F98" t="s">
         <v>42</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M98" t="s">
         <v>36</v>
       </c>
       <c r="T98" s="1"/>
       <c r="V98" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W98" t="s">
         <v>84</v>
@@ -7595,29 +7596,29 @@
         <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D99" t="s">
         <v>280</v>
       </c>
-      <c r="D99" t="s">
-        <v>281</v>
-      </c>
       <c r="E99" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M99" t="s">
         <v>36</v>
       </c>
       <c r="T99" s="1"/>
       <c r="V99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W99" t="s">
         <v>84</v>
@@ -7640,29 +7641,29 @@
         <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D100" t="s">
         <v>282</v>
       </c>
-      <c r="D100" t="s">
-        <v>283</v>
-      </c>
       <c r="E100" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F100" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M100" t="s">
         <v>36</v>
       </c>
       <c r="T100" s="1"/>
       <c r="V100" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W100" t="s">
         <v>84</v>
@@ -7685,29 +7686,29 @@
         <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D101" t="s">
         <v>284</v>
       </c>
-      <c r="D101" t="s">
-        <v>285</v>
-      </c>
       <c r="E101" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F101" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M101" t="s">
         <v>36</v>
       </c>
       <c r="T101" s="1"/>
       <c r="V101" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W101" t="s">
         <v>84</v>
@@ -7730,29 +7731,29 @@
         <v>24</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D102" t="s">
         <v>286</v>
       </c>
-      <c r="D102" t="s">
-        <v>287</v>
-      </c>
       <c r="E102" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F102" t="s">
         <v>42</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M102" t="s">
         <v>36</v>
       </c>
       <c r="T102" s="1"/>
       <c r="V102" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W102" t="s">
         <v>84</v>
@@ -7775,29 +7776,29 @@
         <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D103" t="s">
         <v>288</v>
       </c>
-      <c r="D103" t="s">
-        <v>289</v>
-      </c>
       <c r="E103" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F103" t="s">
         <v>42</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M103" t="s">
         <v>36</v>
       </c>
       <c r="T103" s="1"/>
       <c r="V103" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W103" t="s">
         <v>84</v>
@@ -7820,29 +7821,29 @@
         <v>24</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D104" t="s">
         <v>290</v>
       </c>
-      <c r="D104" t="s">
-        <v>291</v>
-      </c>
       <c r="E104" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M104" t="s">
         <v>36</v>
       </c>
       <c r="T104" s="1"/>
       <c r="V104" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W104" t="s">
         <v>84</v>
@@ -7865,29 +7866,29 @@
         <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D105" t="s">
         <v>292</v>
       </c>
-      <c r="D105" t="s">
-        <v>293</v>
-      </c>
       <c r="E105" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F105" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M105" t="s">
         <v>36</v>
       </c>
       <c r="T105" s="1"/>
       <c r="V105" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W105" t="s">
         <v>84</v>
@@ -7910,29 +7911,29 @@
         <v>24</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106" t="s">
         <v>294</v>
       </c>
-      <c r="D106" t="s">
-        <v>295</v>
-      </c>
       <c r="E106" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M106" t="s">
         <v>36</v>
       </c>
       <c r="T106" s="1"/>
       <c r="V106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W106" t="s">
         <v>84</v>
@@ -7955,29 +7956,29 @@
         <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D107" t="s">
         <v>296</v>
       </c>
-      <c r="D107" t="s">
-        <v>297</v>
-      </c>
       <c r="E107" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F107" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M107" t="s">
         <v>36</v>
       </c>
       <c r="T107" s="1"/>
       <c r="V107" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W107" t="s">
         <v>84</v>
@@ -8000,29 +8001,29 @@
         <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D108" t="s">
         <v>298</v>
       </c>
-      <c r="D108" t="s">
-        <v>299</v>
-      </c>
       <c r="E108" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F108" t="s">
         <v>42</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M108" t="s">
         <v>36</v>
       </c>
       <c r="T108" s="1"/>
       <c r="V108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W108" t="s">
         <v>84</v>
@@ -8045,29 +8046,29 @@
         <v>24</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D109" t="s">
         <v>300</v>
       </c>
-      <c r="D109" t="s">
-        <v>301</v>
-      </c>
       <c r="E109" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F109" t="s">
         <v>42</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M109" t="s">
         <v>36</v>
       </c>
       <c r="T109" s="1"/>
       <c r="V109" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W109" t="s">
         <v>84</v>
@@ -8090,29 +8091,29 @@
         <v>24</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D110" t="s">
+        <v>624</v>
+      </c>
+      <c r="E110" t="s">
         <v>625</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>42</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="F110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="L110" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M110" t="s">
         <v>36</v>
       </c>
       <c r="T110" s="1"/>
       <c r="V110" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W110" t="s">
         <v>84</v>
@@ -8135,31 +8136,31 @@
         <v>24</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D111" t="s">
         <v>303</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>627</v>
+      </c>
+      <c r="F111" t="s">
+        <v>42</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="M111" t="s">
         <v>304</v>
       </c>
-      <c r="E111" t="s">
-        <v>628</v>
-      </c>
-      <c r="F111" t="s">
-        <v>42</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="M111" t="s">
+      <c r="N111" t="s">
         <v>305</v>
       </c>
-      <c r="N111" t="s">
+      <c r="P111" t="s">
         <v>306</v>
-      </c>
-      <c r="P111" t="s">
-        <v>307</v>
       </c>
       <c r="R111" t="s">
         <v>29</v>
@@ -8168,10 +8169,10 @@
         <v>30</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="V111" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="W111" t="s">
         <v>84</v>
@@ -8194,29 +8195,29 @@
         <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D112" t="s">
+        <v>629</v>
+      </c>
+      <c r="E112" t="s">
         <v>630</v>
       </c>
-      <c r="E112" t="s">
-        <v>631</v>
-      </c>
       <c r="F112" t="s">
         <v>42</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M112" t="s">
         <v>36</v>
       </c>
       <c r="T112" s="1"/>
       <c r="V112" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="W112" t="s">
         <v>84</v>
@@ -8239,22 +8240,22 @@
         <v>24</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D113" t="s">
+        <v>631</v>
+      </c>
+      <c r="E113" t="s">
+        <v>631</v>
+      </c>
+      <c r="F113" t="s">
+        <v>42</v>
+      </c>
+      <c r="J113" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="E113" t="s">
-        <v>632</v>
-      </c>
-      <c r="F113" t="s">
-        <v>42</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="L113" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>36</v>
@@ -8262,7 +8263,7 @@
       <c r="P113" s="1"/>
       <c r="T113" s="1"/>
       <c r="V113" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="W113" t="s">
         <v>84</v>
@@ -8285,31 +8286,31 @@
         <v>24</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D114" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E114" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F114" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="N114" t="s">
+        <v>245</v>
+      </c>
+      <c r="P114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="R114" t="s">
         <v>29</v>
@@ -8318,10 +8319,10 @@
         <v>30</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="W114" t="s">
         <v>31</v>
@@ -8333,7 +8334,7 @@
         <v>60</v>
       </c>
       <c r="Z114" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8344,22 +8345,22 @@
         <v>24</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D115" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E115" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F115" t="s">
         <v>42</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>36</v>
@@ -8367,7 +8368,7 @@
       <c r="P115" s="1"/>
       <c r="T115" s="1"/>
       <c r="V115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="W115" t="s">
         <v>84</v>
@@ -8390,25 +8391,25 @@
         <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D116" t="s">
+        <v>634</v>
+      </c>
+      <c r="E116" t="s">
+        <v>634</v>
+      </c>
+      <c r="F116" t="s">
+        <v>42</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="E116" t="s">
-        <v>635</v>
-      </c>
-      <c r="F116" t="s">
-        <v>42</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="M116" t="s">
         <v>36</v>
       </c>
       <c r="V116" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W116" t="s">
         <v>84</v>
@@ -8431,25 +8432,25 @@
         <v>24</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D117" t="s">
+        <v>636</v>
+      </c>
+      <c r="E117" t="s">
+        <v>636</v>
+      </c>
+      <c r="F117" t="s">
+        <v>42</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="E117" t="s">
-        <v>637</v>
-      </c>
-      <c r="F117" t="s">
-        <v>42</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="M117" t="s">
         <v>36</v>
       </c>
       <c r="V117" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W117" t="s">
         <v>84</v>
@@ -8472,25 +8473,25 @@
         <v>24</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
+        <v>638</v>
+      </c>
+      <c r="E118" t="s">
+        <v>638</v>
+      </c>
+      <c r="F118" t="s">
+        <v>42</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E118" t="s">
-        <v>639</v>
-      </c>
-      <c r="F118" t="s">
-        <v>42</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="M118" t="s">
         <v>36</v>
       </c>
       <c r="V118" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W118" t="s">
         <v>84</v>
@@ -8513,25 +8514,25 @@
         <v>24</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D119" t="s">
+        <v>640</v>
+      </c>
+      <c r="E119" t="s">
+        <v>640</v>
+      </c>
+      <c r="F119" t="s">
+        <v>42</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="E119" t="s">
-        <v>641</v>
-      </c>
-      <c r="F119" t="s">
-        <v>42</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="M119" t="s">
         <v>36</v>
       </c>
       <c r="V119" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W119" t="s">
         <v>84</v>
@@ -8554,25 +8555,25 @@
         <v>24</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D120" t="s">
+        <v>642</v>
+      </c>
+      <c r="E120" t="s">
+        <v>642</v>
+      </c>
+      <c r="F120" t="s">
+        <v>42</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="E120" t="s">
-        <v>643</v>
-      </c>
-      <c r="F120" t="s">
-        <v>42</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="M120" t="s">
         <v>36</v>
       </c>
       <c r="V120" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W120" t="s">
         <v>84</v>
@@ -8595,26 +8596,26 @@
         <v>24</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D121" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E121" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F121" t="s">
         <v>42</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M121" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="1"/>
       <c r="V121" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W121" t="s">
         <v>84</v>
@@ -8637,25 +8638,25 @@
         <v>24</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D122" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E122" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F122" t="s">
         <v>42</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M122" t="s">
         <v>36</v>
       </c>
       <c r="V122" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W122" t="s">
         <v>84</v>

--- a/baseline/data_processing_elements-DSE.xlsx
+++ b/baseline/data_processing_elements-DSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\DPE_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FD2AD8-591E-4238-97AE-8549E610F6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E89451C-F1BC-4B83-BB00-DFDC6373EDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4660,7 +4660,7 @@
         <v>50</v>
       </c>
       <c r="Y37" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="Z37" s="8" t="s">
         <v>651</v>
@@ -4722,7 +4722,7 @@
         <v>50</v>
       </c>
       <c r="Y38" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="Z38" s="8" t="s">
         <v>652</v>
